--- a/figures/lecture5/6345.0/634509b.xlsx
+++ b/figures/lecture5/6345.0/634509b.xlsx
@@ -17,404 +17,404 @@
     <sheet name="Enquiries" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="A2638769V">Data1!$R$1:$R$10,Data1!$R$11:$R$114</definedName>
-    <definedName name="A2638769V_Data">Data1!$R$11:$R$114</definedName>
-    <definedName name="A2638769V_Latest">Data1!$R$114</definedName>
-    <definedName name="A2638770C">Data1!$BJ$1:$BJ$10,Data1!$BJ$11:$BJ$114</definedName>
-    <definedName name="A2638770C_Data">Data1!$BJ$11:$BJ$114</definedName>
-    <definedName name="A2638770C_Latest">Data1!$BJ$114</definedName>
-    <definedName name="A2638771F">Data1!$DB$1:$DB$10,Data1!$DB$11:$DB$114</definedName>
-    <definedName name="A2638771F_Data">Data1!$DB$11:$DB$114</definedName>
-    <definedName name="A2638771F_Latest">Data1!$DB$114</definedName>
-    <definedName name="A2638779X">Data1!$H$1:$H$10,Data1!$H$11:$H$114</definedName>
-    <definedName name="A2638779X_Data">Data1!$H$11:$H$114</definedName>
-    <definedName name="A2638779X_Latest">Data1!$H$114</definedName>
-    <definedName name="A2638780J">Data1!$AZ$1:$AZ$10,Data1!$AZ$11:$AZ$114</definedName>
-    <definedName name="A2638780J_Data">Data1!$AZ$11:$AZ$114</definedName>
-    <definedName name="A2638780J_Latest">Data1!$AZ$114</definedName>
-    <definedName name="A2638781K">Data1!$CR$1:$CR$10,Data1!$CR$11:$CR$114</definedName>
-    <definedName name="A2638781K_Data">Data1!$CR$11:$CR$114</definedName>
-    <definedName name="A2638781K_Latest">Data1!$CR$114</definedName>
-    <definedName name="A2638789C">Data1!$P$1:$P$10,Data1!$P$11:$P$114</definedName>
-    <definedName name="A2638789C_Data">Data1!$P$11:$P$114</definedName>
-    <definedName name="A2638789C_Latest">Data1!$P$114</definedName>
-    <definedName name="A2638790L">Data1!$BH$1:$BH$10,Data1!$BH$11:$BH$114</definedName>
-    <definedName name="A2638790L_Data">Data1!$BH$11:$BH$114</definedName>
-    <definedName name="A2638790L_Latest">Data1!$BH$114</definedName>
-    <definedName name="A2638791R">Data1!$CZ$1:$CZ$10,Data1!$CZ$11:$CZ$114</definedName>
-    <definedName name="A2638791R_Data">Data1!$CZ$11:$CZ$114</definedName>
-    <definedName name="A2638791R_Latest">Data1!$CZ$114</definedName>
-    <definedName name="A2638799J">Data1!$K$1:$K$10,Data1!$K$11:$K$114</definedName>
-    <definedName name="A2638799J_Data">Data1!$K$11:$K$114</definedName>
-    <definedName name="A2638799J_Latest">Data1!$K$114</definedName>
-    <definedName name="A2638800F">Data1!$BC$1:$BC$10,Data1!$BC$11:$BC$114</definedName>
-    <definedName name="A2638800F_Data">Data1!$BC$11:$BC$114</definedName>
-    <definedName name="A2638800F_Latest">Data1!$BC$114</definedName>
-    <definedName name="A2638801J">Data1!$CU$1:$CU$10,Data1!$CU$11:$CU$114</definedName>
-    <definedName name="A2638801J_Data">Data1!$CU$11:$CU$114</definedName>
-    <definedName name="A2638801J_Latest">Data1!$CU$114</definedName>
-    <definedName name="A2638809A">Data1!$I$1:$I$10,Data1!$I$11:$I$114</definedName>
-    <definedName name="A2638809A_Data">Data1!$I$11:$I$114</definedName>
-    <definedName name="A2638809A_Latest">Data1!$I$114</definedName>
-    <definedName name="A2638810K">Data1!$BA$1:$BA$10,Data1!$BA$11:$BA$114</definedName>
-    <definedName name="A2638810K_Data">Data1!$BA$11:$BA$114</definedName>
-    <definedName name="A2638810K_Latest">Data1!$BA$114</definedName>
-    <definedName name="A2638811L">Data1!$CS$1:$CS$10,Data1!$CS$11:$CS$114</definedName>
-    <definedName name="A2638811L_Data">Data1!$CS$11:$CS$114</definedName>
-    <definedName name="A2638811L_Latest">Data1!$CS$114</definedName>
-    <definedName name="A2638819F">Data1!$M$1:$M$10,Data1!$M$11:$M$114</definedName>
-    <definedName name="A2638819F_Data">Data1!$M$11:$M$114</definedName>
-    <definedName name="A2638819F_Latest">Data1!$M$114</definedName>
-    <definedName name="A2638820R">Data1!$BE$1:$BE$10,Data1!$BE$11:$BE$114</definedName>
-    <definedName name="A2638820R_Data">Data1!$BE$11:$BE$114</definedName>
-    <definedName name="A2638820R_Latest">Data1!$BE$114</definedName>
-    <definedName name="A2638821T">Data1!$CW$1:$CW$10,Data1!$CW$11:$CW$114</definedName>
-    <definedName name="A2638821T_Data">Data1!$CW$11:$CW$114</definedName>
-    <definedName name="A2638821T_Latest">Data1!$CW$114</definedName>
-    <definedName name="A2638829K">Data1!$D$1:$D$10,Data1!$D$11:$D$114</definedName>
-    <definedName name="A2638829K_Data">Data1!$D$11:$D$114</definedName>
-    <definedName name="A2638829K_Latest">Data1!$D$114</definedName>
-    <definedName name="A2638830V">Data1!$AV$1:$AV$10,Data1!$AV$11:$AV$114</definedName>
-    <definedName name="A2638830V_Data">Data1!$AV$11:$AV$114</definedName>
-    <definedName name="A2638830V_Latest">Data1!$AV$114</definedName>
-    <definedName name="A2638831W">Data1!$CN$1:$CN$10,Data1!$CN$11:$CN$114</definedName>
-    <definedName name="A2638831W_Data">Data1!$CN$11:$CN$114</definedName>
-    <definedName name="A2638831W_Latest">Data1!$CN$114</definedName>
-    <definedName name="A2638839R">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$114</definedName>
-    <definedName name="A2638839R_Data">Data1!$Q$11:$Q$114</definedName>
-    <definedName name="A2638839R_Latest">Data1!$Q$114</definedName>
-    <definedName name="A2638840X">Data1!$BI$1:$BI$10,Data1!$BI$11:$BI$114</definedName>
-    <definedName name="A2638840X_Data">Data1!$BI$11:$BI$114</definedName>
-    <definedName name="A2638840X_Latest">Data1!$BI$114</definedName>
-    <definedName name="A2638841A">Data1!$DA$1:$DA$10,Data1!$DA$11:$DA$114</definedName>
-    <definedName name="A2638841A_Data">Data1!$DA$11:$DA$114</definedName>
-    <definedName name="A2638841A_Latest">Data1!$DA$114</definedName>
-    <definedName name="A2638849V">Data1!$B$1:$B$10,Data1!$B$11:$B$114</definedName>
-    <definedName name="A2638849V_Data">Data1!$B$11:$B$114</definedName>
-    <definedName name="A2638849V_Latest">Data1!$B$114</definedName>
-    <definedName name="A2638850C">Data1!$AT$1:$AT$10,Data1!$AT$11:$AT$114</definedName>
-    <definedName name="A2638850C_Data">Data1!$AT$11:$AT$114</definedName>
-    <definedName name="A2638850C_Latest">Data1!$AT$114</definedName>
-    <definedName name="A2638851F">Data1!$CL$1:$CL$10,Data1!$CL$11:$CL$114</definedName>
-    <definedName name="A2638851F_Data">Data1!$CL$11:$CL$114</definedName>
-    <definedName name="A2638851F_Latest">Data1!$CL$114</definedName>
-    <definedName name="A2638859X">Data1!$J$1:$J$10,Data1!$J$11:$J$114</definedName>
-    <definedName name="A2638859X_Data">Data1!$J$11:$J$114</definedName>
-    <definedName name="A2638859X_Latest">Data1!$J$114</definedName>
-    <definedName name="A2638860J">Data1!$BB$1:$BB$10,Data1!$BB$11:$BB$114</definedName>
-    <definedName name="A2638860J_Data">Data1!$BB$11:$BB$114</definedName>
-    <definedName name="A2638860J_Latest">Data1!$BB$114</definedName>
-    <definedName name="A2638861K">Data1!$CT$1:$CT$10,Data1!$CT$11:$CT$114</definedName>
-    <definedName name="A2638861K_Data">Data1!$CT$11:$CT$114</definedName>
-    <definedName name="A2638861K_Latest">Data1!$CT$114</definedName>
-    <definedName name="A2638869C">Data1!$C$1:$C$10,Data1!$C$11:$C$114</definedName>
-    <definedName name="A2638869C_Data">Data1!$C$11:$C$114</definedName>
-    <definedName name="A2638869C_Latest">Data1!$C$114</definedName>
-    <definedName name="A2638870L">Data1!$AU$1:$AU$10,Data1!$AU$11:$AU$114</definedName>
-    <definedName name="A2638870L_Data">Data1!$AU$11:$AU$114</definedName>
-    <definedName name="A2638870L_Latest">Data1!$AU$114</definedName>
-    <definedName name="A2638871R">Data1!$CM$1:$CM$10,Data1!$CM$11:$CM$114</definedName>
-    <definedName name="A2638871R_Data">Data1!$CM$11:$CM$114</definedName>
-    <definedName name="A2638871R_Latest">Data1!$CM$114</definedName>
-    <definedName name="A2638879J">Data1!$N$1:$N$10,Data1!$N$11:$N$114</definedName>
-    <definedName name="A2638879J_Data">Data1!$N$11:$N$114</definedName>
-    <definedName name="A2638879J_Latest">Data1!$N$114</definedName>
-    <definedName name="A2638880T">Data1!$BF$1:$BF$10,Data1!$BF$11:$BF$114</definedName>
-    <definedName name="A2638880T_Data">Data1!$BF$11:$BF$114</definedName>
-    <definedName name="A2638880T_Latest">Data1!$BF$114</definedName>
-    <definedName name="A2638881V">Data1!$CX$1:$CX$10,Data1!$CX$11:$CX$114</definedName>
-    <definedName name="A2638881V_Data">Data1!$CX$11:$CX$114</definedName>
-    <definedName name="A2638881V_Latest">Data1!$CX$114</definedName>
-    <definedName name="A2638889L">Data1!$O$1:$O$10,Data1!$O$11:$O$114</definedName>
-    <definedName name="A2638889L_Data">Data1!$O$11:$O$114</definedName>
-    <definedName name="A2638889L_Latest">Data1!$O$114</definedName>
-    <definedName name="A2638890W">Data1!$BG$1:$BG$10,Data1!$BG$11:$BG$114</definedName>
-    <definedName name="A2638890W_Data">Data1!$BG$11:$BG$114</definedName>
-    <definedName name="A2638890W_Latest">Data1!$BG$114</definedName>
-    <definedName name="A2638891X">Data1!$CY$1:$CY$10,Data1!$CY$11:$CY$114</definedName>
-    <definedName name="A2638891X_Data">Data1!$CY$11:$CY$114</definedName>
-    <definedName name="A2638891X_Latest">Data1!$CY$114</definedName>
-    <definedName name="A2638899T">Data1!$G$1:$G$10,Data1!$G$11:$G$114</definedName>
-    <definedName name="A2638899T_Data">Data1!$G$11:$G$114</definedName>
-    <definedName name="A2638899T_Latest">Data1!$G$114</definedName>
-    <definedName name="A2638900R">Data1!$AY$1:$AY$10,Data1!$AY$11:$AY$114</definedName>
-    <definedName name="A2638900R_Data">Data1!$AY$11:$AY$114</definedName>
-    <definedName name="A2638900R_Latest">Data1!$AY$114</definedName>
-    <definedName name="A2638901T">Data1!$CQ$1:$CQ$10,Data1!$CQ$11:$CQ$114</definedName>
-    <definedName name="A2638901T_Data">Data1!$CQ$11:$CQ$114</definedName>
-    <definedName name="A2638901T_Latest">Data1!$CQ$114</definedName>
-    <definedName name="A2638909K">Data1!$F$1:$F$10,Data1!$F$11:$F$114</definedName>
-    <definedName name="A2638909K_Data">Data1!$F$11:$F$114</definedName>
-    <definedName name="A2638909K_Latest">Data1!$F$114</definedName>
-    <definedName name="A2638910V">Data1!$AX$1:$AX$10,Data1!$AX$11:$AX$114</definedName>
-    <definedName name="A2638910V_Data">Data1!$AX$11:$AX$114</definedName>
-    <definedName name="A2638910V_Latest">Data1!$AX$114</definedName>
-    <definedName name="A2638911W">Data1!$CP$1:$CP$10,Data1!$CP$11:$CP$114</definedName>
-    <definedName name="A2638911W_Data">Data1!$CP$11:$CP$114</definedName>
-    <definedName name="A2638911W_Latest">Data1!$CP$114</definedName>
-    <definedName name="A2638919R">Data1!$S$1:$S$10,Data1!$S$11:$S$114</definedName>
-    <definedName name="A2638919R_Data">Data1!$S$11:$S$114</definedName>
-    <definedName name="A2638919R_Latest">Data1!$S$114</definedName>
-    <definedName name="A2638920X">Data1!$BK$1:$BK$10,Data1!$BK$11:$BK$114</definedName>
-    <definedName name="A2638920X_Data">Data1!$BK$11:$BK$114</definedName>
-    <definedName name="A2638920X_Latest">Data1!$BK$114</definedName>
-    <definedName name="A2638921A">Data1!$DC$1:$DC$10,Data1!$DC$11:$DC$114</definedName>
-    <definedName name="A2638921A_Data">Data1!$DC$11:$DC$114</definedName>
-    <definedName name="A2638921A_Latest">Data1!$DC$114</definedName>
-    <definedName name="A2638929V">Data1!$E$1:$E$10,Data1!$E$11:$E$114</definedName>
-    <definedName name="A2638929V_Data">Data1!$E$11:$E$114</definedName>
-    <definedName name="A2638929V_Latest">Data1!$E$114</definedName>
-    <definedName name="A2638930C">Data1!$AW$1:$AW$10,Data1!$AW$11:$AW$114</definedName>
-    <definedName name="A2638930C_Data">Data1!$AW$11:$AW$114</definedName>
-    <definedName name="A2638930C_Latest">Data1!$AW$114</definedName>
-    <definedName name="A2638931F">Data1!$CO$1:$CO$10,Data1!$CO$11:$CO$114</definedName>
-    <definedName name="A2638931F_Data">Data1!$CO$11:$CO$114</definedName>
-    <definedName name="A2638931F_Latest">Data1!$CO$114</definedName>
-    <definedName name="A2638939X">Data1!$L$1:$L$10,Data1!$L$11:$L$114</definedName>
-    <definedName name="A2638939X_Data">Data1!$L$11:$L$114</definedName>
-    <definedName name="A2638939X_Latest">Data1!$L$114</definedName>
-    <definedName name="A2638940J">Data1!$BD$1:$BD$10,Data1!$BD$11:$BD$114</definedName>
-    <definedName name="A2638940J_Data">Data1!$BD$11:$BD$114</definedName>
-    <definedName name="A2638940J_Latest">Data1!$BD$114</definedName>
-    <definedName name="A2638941K">Data1!$CV$1:$CV$10,Data1!$CV$11:$CV$114</definedName>
-    <definedName name="A2638941K_Data">Data1!$CV$11:$CV$114</definedName>
-    <definedName name="A2638941K_Latest">Data1!$CV$114</definedName>
-    <definedName name="A2638949C">Data1!$T$1:$T$10,Data1!$T$11:$T$114</definedName>
-    <definedName name="A2638949C_Data">Data1!$T$11:$T$114</definedName>
-    <definedName name="A2638949C_Latest">Data1!$T$114</definedName>
-    <definedName name="A2638950L">Data1!$BL$1:$BL$10,Data1!$BL$11:$BL$114</definedName>
-    <definedName name="A2638950L_Data">Data1!$BL$11:$BL$114</definedName>
-    <definedName name="A2638950L_Latest">Data1!$BL$114</definedName>
-    <definedName name="A2638951R">Data1!$DD$1:$DD$10,Data1!$DD$11:$DD$114</definedName>
-    <definedName name="A2638951R_Data">Data1!$DD$11:$DD$114</definedName>
-    <definedName name="A2638951R_Latest">Data1!$DD$114</definedName>
-    <definedName name="A2639339L">Data1!$AQ$1:$AQ$10,Data1!$AQ$11:$AQ$114</definedName>
-    <definedName name="A2639339L_Data">Data1!$AQ$11:$AQ$114</definedName>
-    <definedName name="A2639339L_Latest">Data1!$AQ$114</definedName>
-    <definedName name="A2639340W">Data1!$CI$1:$CI$10,Data1!$CI$11:$CI$114</definedName>
-    <definedName name="A2639340W_Data">Data1!$CI$11:$CI$114</definedName>
-    <definedName name="A2639340W_Latest">Data1!$CI$114</definedName>
-    <definedName name="A2639341X">Data1!$EA$1:$EA$10,Data1!$EA$11:$EA$114</definedName>
-    <definedName name="A2639341X_Data">Data1!$EA$11:$EA$114</definedName>
-    <definedName name="A2639341X_Latest">Data1!$EA$114</definedName>
-    <definedName name="A2639349T">Data1!$AG$1:$AG$10,Data1!$AG$11:$AG$114</definedName>
-    <definedName name="A2639349T_Data">Data1!$AG$11:$AG$114</definedName>
-    <definedName name="A2639349T_Latest">Data1!$AG$114</definedName>
-    <definedName name="A2639350A">Data1!$BY$1:$BY$10,Data1!$BY$11:$BY$114</definedName>
-    <definedName name="A2639350A_Data">Data1!$BY$11:$BY$114</definedName>
-    <definedName name="A2639350A_Latest">Data1!$BY$114</definedName>
-    <definedName name="A2639351C">Data1!$DQ$1:$DQ$10,Data1!$DQ$11:$DQ$114</definedName>
-    <definedName name="A2639351C_Data">Data1!$DQ$11:$DQ$114</definedName>
-    <definedName name="A2639351C_Latest">Data1!$DQ$114</definedName>
-    <definedName name="A2639359W">Data1!$AO$1:$AO$10,Data1!$AO$11:$AO$114</definedName>
-    <definedName name="A2639359W_Data">Data1!$AO$11:$AO$114</definedName>
-    <definedName name="A2639359W_Latest">Data1!$AO$114</definedName>
-    <definedName name="A2639360F">Data1!$CG$1:$CG$10,Data1!$CG$11:$CG$114</definedName>
-    <definedName name="A2639360F_Data">Data1!$CG$11:$CG$114</definedName>
-    <definedName name="A2639360F_Latest">Data1!$CG$114</definedName>
-    <definedName name="A2639361J">Data1!$DY$1:$DY$10,Data1!$DY$11:$DY$114</definedName>
-    <definedName name="A2639361J_Data">Data1!$DY$11:$DY$114</definedName>
-    <definedName name="A2639361J_Latest">Data1!$DY$114</definedName>
-    <definedName name="A2639369A">Data1!$AJ$1:$AJ$10,Data1!$AJ$11:$AJ$114</definedName>
-    <definedName name="A2639369A_Data">Data1!$AJ$11:$AJ$114</definedName>
-    <definedName name="A2639369A_Latest">Data1!$AJ$114</definedName>
-    <definedName name="A2639370K">Data1!$CB$1:$CB$10,Data1!$CB$11:$CB$114</definedName>
-    <definedName name="A2639370K_Data">Data1!$CB$11:$CB$114</definedName>
-    <definedName name="A2639370K_Latest">Data1!$CB$114</definedName>
-    <definedName name="A2639371L">Data1!$DT$1:$DT$10,Data1!$DT$11:$DT$114</definedName>
-    <definedName name="A2639371L_Data">Data1!$DT$11:$DT$114</definedName>
-    <definedName name="A2639371L_Latest">Data1!$DT$114</definedName>
-    <definedName name="A2639379F">Data1!$AH$1:$AH$10,Data1!$AH$11:$AH$114</definedName>
-    <definedName name="A2639379F_Data">Data1!$AH$11:$AH$114</definedName>
-    <definedName name="A2639379F_Latest">Data1!$AH$114</definedName>
-    <definedName name="A2639380R">Data1!$BZ$1:$BZ$10,Data1!$BZ$11:$BZ$114</definedName>
-    <definedName name="A2639380R_Data">Data1!$BZ$11:$BZ$114</definedName>
-    <definedName name="A2639380R_Latest">Data1!$BZ$114</definedName>
-    <definedName name="A2639381T">Data1!$DR$1:$DR$10,Data1!$DR$11:$DR$114</definedName>
-    <definedName name="A2639381T_Data">Data1!$DR$11:$DR$114</definedName>
-    <definedName name="A2639381T_Latest">Data1!$DR$114</definedName>
-    <definedName name="A2639389K">Data1!$AL$1:$AL$10,Data1!$AL$11:$AL$114</definedName>
-    <definedName name="A2639389K_Data">Data1!$AL$11:$AL$114</definedName>
-    <definedName name="A2639389K_Latest">Data1!$AL$114</definedName>
-    <definedName name="A2639390V">Data1!$CD$1:$CD$10,Data1!$CD$11:$CD$114</definedName>
-    <definedName name="A2639390V_Data">Data1!$CD$11:$CD$114</definedName>
-    <definedName name="A2639390V_Latest">Data1!$CD$114</definedName>
-    <definedName name="A2639391W">Data1!$DV$1:$DV$10,Data1!$DV$11:$DV$114</definedName>
-    <definedName name="A2639391W_Data">Data1!$DV$11:$DV$114</definedName>
-    <definedName name="A2639391W_Latest">Data1!$DV$114</definedName>
-    <definedName name="A2639399R">Data1!$AC$1:$AC$10,Data1!$AC$11:$AC$114</definedName>
-    <definedName name="A2639399R_Data">Data1!$AC$11:$AC$114</definedName>
-    <definedName name="A2639399R_Latest">Data1!$AC$114</definedName>
-    <definedName name="A2639400L">Data1!$BU$1:$BU$10,Data1!$BU$11:$BU$114</definedName>
-    <definedName name="A2639400L_Data">Data1!$BU$11:$BU$114</definedName>
-    <definedName name="A2639400L_Latest">Data1!$BU$114</definedName>
-    <definedName name="A2639401R">Data1!$DM$1:$DM$10,Data1!$DM$11:$DM$114</definedName>
-    <definedName name="A2639401R_Data">Data1!$DM$11:$DM$114</definedName>
-    <definedName name="A2639401R_Latest">Data1!$DM$114</definedName>
-    <definedName name="A2639409J">Data1!$AP$1:$AP$10,Data1!$AP$11:$AP$114</definedName>
-    <definedName name="A2639409J_Data">Data1!$AP$11:$AP$114</definedName>
-    <definedName name="A2639409J_Latest">Data1!$AP$114</definedName>
-    <definedName name="A2639410T">Data1!$CH$1:$CH$10,Data1!$CH$11:$CH$114</definedName>
-    <definedName name="A2639410T_Data">Data1!$CH$11:$CH$114</definedName>
-    <definedName name="A2639410T_Latest">Data1!$CH$114</definedName>
-    <definedName name="A2639411V">Data1!$DZ$1:$DZ$10,Data1!$DZ$11:$DZ$114</definedName>
-    <definedName name="A2639411V_Data">Data1!$DZ$11:$DZ$114</definedName>
-    <definedName name="A2639411V_Latest">Data1!$DZ$114</definedName>
-    <definedName name="A2639419L">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$114</definedName>
-    <definedName name="A2639419L_Data">Data1!$AA$11:$AA$114</definedName>
-    <definedName name="A2639419L_Latest">Data1!$AA$114</definedName>
-    <definedName name="A2639420W">Data1!$BS$1:$BS$10,Data1!$BS$11:$BS$114</definedName>
-    <definedName name="A2639420W_Data">Data1!$BS$11:$BS$114</definedName>
-    <definedName name="A2639420W_Latest">Data1!$BS$114</definedName>
-    <definedName name="A2639421X">Data1!$DK$1:$DK$10,Data1!$DK$11:$DK$114</definedName>
-    <definedName name="A2639421X_Data">Data1!$DK$11:$DK$114</definedName>
-    <definedName name="A2639421X_Latest">Data1!$DK$114</definedName>
-    <definedName name="A2639429T">Data1!$AI$1:$AI$10,Data1!$AI$11:$AI$114</definedName>
-    <definedName name="A2639429T_Data">Data1!$AI$11:$AI$114</definedName>
-    <definedName name="A2639429T_Latest">Data1!$AI$114</definedName>
-    <definedName name="A2639430A">Data1!$CA$1:$CA$10,Data1!$CA$11:$CA$114</definedName>
-    <definedName name="A2639430A_Data">Data1!$CA$11:$CA$114</definedName>
-    <definedName name="A2639430A_Latest">Data1!$CA$114</definedName>
-    <definedName name="A2639431C">Data1!$DS$1:$DS$10,Data1!$DS$11:$DS$114</definedName>
-    <definedName name="A2639431C_Data">Data1!$DS$11:$DS$114</definedName>
-    <definedName name="A2639431C_Latest">Data1!$DS$114</definedName>
-    <definedName name="A2639439W">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$114</definedName>
-    <definedName name="A2639439W_Data">Data1!$AB$11:$AB$114</definedName>
-    <definedName name="A2639439W_Latest">Data1!$AB$114</definedName>
-    <definedName name="A2639440F">Data1!$BT$1:$BT$10,Data1!$BT$11:$BT$114</definedName>
-    <definedName name="A2639440F_Data">Data1!$BT$11:$BT$114</definedName>
-    <definedName name="A2639440F_Latest">Data1!$BT$114</definedName>
-    <definedName name="A2639441J">Data1!$DL$1:$DL$10,Data1!$DL$11:$DL$114</definedName>
-    <definedName name="A2639441J_Data">Data1!$DL$11:$DL$114</definedName>
-    <definedName name="A2639441J_Latest">Data1!$DL$114</definedName>
-    <definedName name="A2639449A">Data1!$AM$1:$AM$10,Data1!$AM$11:$AM$114</definedName>
-    <definedName name="A2639449A_Data">Data1!$AM$11:$AM$114</definedName>
-    <definedName name="A2639449A_Latest">Data1!$AM$114</definedName>
-    <definedName name="A2639450K">Data1!$CE$1:$CE$10,Data1!$CE$11:$CE$114</definedName>
-    <definedName name="A2639450K_Data">Data1!$CE$11:$CE$114</definedName>
-    <definedName name="A2639450K_Latest">Data1!$CE$114</definedName>
-    <definedName name="A2639451L">Data1!$DW$1:$DW$10,Data1!$DW$11:$DW$114</definedName>
-    <definedName name="A2639451L_Data">Data1!$DW$11:$DW$114</definedName>
-    <definedName name="A2639451L_Latest">Data1!$DW$114</definedName>
-    <definedName name="A2639459F">Data1!$AN$1:$AN$10,Data1!$AN$11:$AN$114</definedName>
-    <definedName name="A2639459F_Data">Data1!$AN$11:$AN$114</definedName>
-    <definedName name="A2639459F_Latest">Data1!$AN$114</definedName>
-    <definedName name="A2639460R">Data1!$CF$1:$CF$10,Data1!$CF$11:$CF$114</definedName>
-    <definedName name="A2639460R_Data">Data1!$CF$11:$CF$114</definedName>
-    <definedName name="A2639460R_Latest">Data1!$CF$114</definedName>
-    <definedName name="A2639461T">Data1!$DX$1:$DX$10,Data1!$DX$11:$DX$114</definedName>
-    <definedName name="A2639461T_Data">Data1!$DX$11:$DX$114</definedName>
-    <definedName name="A2639461T_Latest">Data1!$DX$114</definedName>
-    <definedName name="A2639469K">Data1!$AF$1:$AF$10,Data1!$AF$11:$AF$114</definedName>
-    <definedName name="A2639469K_Data">Data1!$AF$11:$AF$114</definedName>
-    <definedName name="A2639469K_Latest">Data1!$AF$114</definedName>
-    <definedName name="A2639470V">Data1!$BX$1:$BX$10,Data1!$BX$11:$BX$114</definedName>
-    <definedName name="A2639470V_Data">Data1!$BX$11:$BX$114</definedName>
-    <definedName name="A2639470V_Latest">Data1!$BX$114</definedName>
-    <definedName name="A2639471W">Data1!$DP$1:$DP$10,Data1!$DP$11:$DP$114</definedName>
-    <definedName name="A2639471W_Data">Data1!$DP$11:$DP$114</definedName>
-    <definedName name="A2639471W_Latest">Data1!$DP$114</definedName>
-    <definedName name="A2639479R">Data1!$AE$1:$AE$10,Data1!$AE$11:$AE$114</definedName>
-    <definedName name="A2639479R_Data">Data1!$AE$11:$AE$114</definedName>
-    <definedName name="A2639479R_Latest">Data1!$AE$114</definedName>
-    <definedName name="A2639480X">Data1!$BW$1:$BW$10,Data1!$BW$11:$BW$114</definedName>
-    <definedName name="A2639480X_Data">Data1!$BW$11:$BW$114</definedName>
-    <definedName name="A2639480X_Latest">Data1!$BW$114</definedName>
-    <definedName name="A2639481A">Data1!$DO$1:$DO$10,Data1!$DO$11:$DO$114</definedName>
-    <definedName name="A2639481A_Data">Data1!$DO$11:$DO$114</definedName>
-    <definedName name="A2639481A_Latest">Data1!$DO$114</definedName>
-    <definedName name="A2639489V">Data1!$AR$1:$AR$10,Data1!$AR$11:$AR$114</definedName>
-    <definedName name="A2639489V_Data">Data1!$AR$11:$AR$114</definedName>
-    <definedName name="A2639489V_Latest">Data1!$AR$114</definedName>
-    <definedName name="A2639490C">Data1!$CJ$1:$CJ$10,Data1!$CJ$11:$CJ$114</definedName>
-    <definedName name="A2639490C_Data">Data1!$CJ$11:$CJ$114</definedName>
-    <definedName name="A2639490C_Latest">Data1!$CJ$114</definedName>
-    <definedName name="A2639491F">Data1!$EB$1:$EB$10,Data1!$EB$11:$EB$114</definedName>
-    <definedName name="A2639491F_Data">Data1!$EB$11:$EB$114</definedName>
-    <definedName name="A2639491F_Latest">Data1!$EB$114</definedName>
-    <definedName name="A2639499X">Data1!$AD$1:$AD$10,Data1!$AD$11:$AD$114</definedName>
-    <definedName name="A2639499X_Data">Data1!$AD$11:$AD$114</definedName>
-    <definedName name="A2639499X_Latest">Data1!$AD$114</definedName>
-    <definedName name="A2639500W">Data1!$BV$1:$BV$10,Data1!$BV$11:$BV$114</definedName>
-    <definedName name="A2639500W_Data">Data1!$BV$11:$BV$114</definedName>
-    <definedName name="A2639500W_Latest">Data1!$BV$114</definedName>
-    <definedName name="A2639501X">Data1!$DN$1:$DN$10,Data1!$DN$11:$DN$114</definedName>
-    <definedName name="A2639501X_Data">Data1!$DN$11:$DN$114</definedName>
-    <definedName name="A2639501X_Latest">Data1!$DN$114</definedName>
-    <definedName name="A2639509T">Data1!$AK$1:$AK$10,Data1!$AK$11:$AK$114</definedName>
-    <definedName name="A2639509T_Data">Data1!$AK$11:$AK$114</definedName>
-    <definedName name="A2639509T_Latest">Data1!$AK$114</definedName>
-    <definedName name="A2639510A">Data1!$CC$1:$CC$10,Data1!$CC$11:$CC$114</definedName>
-    <definedName name="A2639510A_Data">Data1!$CC$11:$CC$114</definedName>
-    <definedName name="A2639510A_Latest">Data1!$CC$114</definedName>
-    <definedName name="A2639511C">Data1!$DU$1:$DU$10,Data1!$DU$11:$DU$114</definedName>
-    <definedName name="A2639511C_Data">Data1!$DU$11:$DU$114</definedName>
-    <definedName name="A2639511C_Latest">Data1!$DU$114</definedName>
-    <definedName name="A2639519W">Data1!$AS$1:$AS$10,Data1!$AS$11:$AS$114</definedName>
-    <definedName name="A2639519W_Data">Data1!$AS$11:$AS$114</definedName>
-    <definedName name="A2639519W_Latest">Data1!$AS$114</definedName>
-    <definedName name="A2639520F">Data1!$CK$1:$CK$10,Data1!$CK$11:$CK$114</definedName>
-    <definedName name="A2639520F_Data">Data1!$CK$11:$CK$114</definedName>
-    <definedName name="A2639520F_Latest">Data1!$CK$114</definedName>
-    <definedName name="A2639521J">Data1!$EC$1:$EC$10,Data1!$EC$11:$EC$114</definedName>
-    <definedName name="A2639521J_Data">Data1!$EC$11:$EC$114</definedName>
-    <definedName name="A2639521J_Latest">Data1!$EC$114</definedName>
-    <definedName name="A2639739X">Data1!$X$1:$X$10,Data1!$X$11:$X$114</definedName>
-    <definedName name="A2639739X_Data">Data1!$X$11:$X$114</definedName>
-    <definedName name="A2639739X_Latest">Data1!$X$114</definedName>
-    <definedName name="A2639740J">Data1!$BP$1:$BP$10,Data1!$BP$11:$BP$114</definedName>
-    <definedName name="A2639740J_Data">Data1!$BP$11:$BP$114</definedName>
-    <definedName name="A2639740J_Latest">Data1!$BP$114</definedName>
-    <definedName name="A2639741K">Data1!$DH$1:$DH$10,Data1!$DH$11:$DH$114</definedName>
-    <definedName name="A2639741K_Data">Data1!$DH$11:$DH$114</definedName>
-    <definedName name="A2639741K_Latest">Data1!$DH$114</definedName>
-    <definedName name="A2639769L">Data1!$V$1:$V$10,Data1!$V$11:$V$114</definedName>
-    <definedName name="A2639769L_Data">Data1!$V$11:$V$114</definedName>
-    <definedName name="A2639769L_Latest">Data1!$V$114</definedName>
-    <definedName name="A2639770W">Data1!$BN$1:$BN$10,Data1!$BN$11:$BN$114</definedName>
-    <definedName name="A2639770W_Data">Data1!$BN$11:$BN$114</definedName>
-    <definedName name="A2639770W_Latest">Data1!$BN$114</definedName>
-    <definedName name="A2639771X">Data1!$DF$1:$DF$10,Data1!$DF$11:$DF$114</definedName>
-    <definedName name="A2639771X_Data">Data1!$DF$11:$DF$114</definedName>
-    <definedName name="A2639771X_Latest">Data1!$DF$114</definedName>
-    <definedName name="A2639779T">Data1!$U$1:$U$10,Data1!$U$11:$U$114</definedName>
-    <definedName name="A2639779T_Data">Data1!$U$11:$U$114</definedName>
-    <definedName name="A2639779T_Latest">Data1!$U$114</definedName>
-    <definedName name="A2639780A">Data1!$BM$1:$BM$10,Data1!$BM$11:$BM$114</definedName>
-    <definedName name="A2639780A_Data">Data1!$BM$11:$BM$114</definedName>
-    <definedName name="A2639780A_Latest">Data1!$BM$114</definedName>
-    <definedName name="A2639781C">Data1!$DE$1:$DE$10,Data1!$DE$11:$DE$114</definedName>
-    <definedName name="A2639781C_Data">Data1!$DE$11:$DE$114</definedName>
-    <definedName name="A2639781C_Latest">Data1!$DE$114</definedName>
-    <definedName name="A2639789W">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$114</definedName>
-    <definedName name="A2639789W_Data">Data1!$Y$11:$Y$114</definedName>
-    <definedName name="A2639789W_Latest">Data1!$Y$114</definedName>
-    <definedName name="A2639790F">Data1!$BQ$1:$BQ$10,Data1!$BQ$11:$BQ$114</definedName>
-    <definedName name="A2639790F_Data">Data1!$BQ$11:$BQ$114</definedName>
-    <definedName name="A2639790F_Latest">Data1!$BQ$114</definedName>
-    <definedName name="A2639791J">Data1!$DI$1:$DI$10,Data1!$DI$11:$DI$114</definedName>
-    <definedName name="A2639791J_Data">Data1!$DI$11:$DI$114</definedName>
-    <definedName name="A2639791J_Latest">Data1!$DI$114</definedName>
-    <definedName name="A2639839J">Data1!$W$1:$W$10,Data1!$W$11:$W$114</definedName>
-    <definedName name="A2639839J_Data">Data1!$W$11:$W$114</definedName>
-    <definedName name="A2639839J_Latest">Data1!$W$114</definedName>
-    <definedName name="A2639840T">Data1!$BO$1:$BO$10,Data1!$BO$11:$BO$114</definedName>
-    <definedName name="A2639840T_Data">Data1!$BO$11:$BO$114</definedName>
-    <definedName name="A2639840T_Latest">Data1!$BO$114</definedName>
-    <definedName name="A2639841V">Data1!$DG$1:$DG$10,Data1!$DG$11:$DG$114</definedName>
-    <definedName name="A2639841V_Data">Data1!$DG$11:$DG$114</definedName>
-    <definedName name="A2639841V_Latest">Data1!$DG$114</definedName>
-    <definedName name="A2639899K">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$114</definedName>
-    <definedName name="A2639899K_Data">Data1!$Z$11:$Z$114</definedName>
-    <definedName name="A2639899K_Latest">Data1!$Z$114</definedName>
-    <definedName name="A2639900J">Data1!$BR$1:$BR$10,Data1!$BR$11:$BR$114</definedName>
-    <definedName name="A2639900J_Data">Data1!$BR$11:$BR$114</definedName>
-    <definedName name="A2639900J_Latest">Data1!$BR$114</definedName>
-    <definedName name="A2639901K">Data1!$DJ$1:$DJ$10,Data1!$DJ$11:$DJ$114</definedName>
-    <definedName name="A2639901K_Data">Data1!$DJ$11:$DJ$114</definedName>
-    <definedName name="A2639901K_Latest">Data1!$DJ$114</definedName>
-    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$114</definedName>
-    <definedName name="Date_Range_Data">Data1!$A$11:$A$114</definedName>
+    <definedName name="A2638769V">Data1!$R$1:$R$10,Data1!$R$11:$R$124</definedName>
+    <definedName name="A2638769V_Data">Data1!$R$11:$R$124</definedName>
+    <definedName name="A2638769V_Latest">Data1!$R$124</definedName>
+    <definedName name="A2638770C">Data1!$BJ$1:$BJ$10,Data1!$BJ$11:$BJ$124</definedName>
+    <definedName name="A2638770C_Data">Data1!$BJ$11:$BJ$124</definedName>
+    <definedName name="A2638770C_Latest">Data1!$BJ$124</definedName>
+    <definedName name="A2638771F">Data1!$DB$1:$DB$10,Data1!$DB$11:$DB$124</definedName>
+    <definedName name="A2638771F_Data">Data1!$DB$11:$DB$124</definedName>
+    <definedName name="A2638771F_Latest">Data1!$DB$124</definedName>
+    <definedName name="A2638779X">Data1!$H$1:$H$10,Data1!$H$11:$H$124</definedName>
+    <definedName name="A2638779X_Data">Data1!$H$11:$H$124</definedName>
+    <definedName name="A2638779X_Latest">Data1!$H$124</definedName>
+    <definedName name="A2638780J">Data1!$AZ$1:$AZ$10,Data1!$AZ$11:$AZ$124</definedName>
+    <definedName name="A2638780J_Data">Data1!$AZ$11:$AZ$124</definedName>
+    <definedName name="A2638780J_Latest">Data1!$AZ$124</definedName>
+    <definedName name="A2638781K">Data1!$CR$1:$CR$10,Data1!$CR$11:$CR$124</definedName>
+    <definedName name="A2638781K_Data">Data1!$CR$11:$CR$124</definedName>
+    <definedName name="A2638781K_Latest">Data1!$CR$124</definedName>
+    <definedName name="A2638789C">Data1!$P$1:$P$10,Data1!$P$11:$P$124</definedName>
+    <definedName name="A2638789C_Data">Data1!$P$11:$P$124</definedName>
+    <definedName name="A2638789C_Latest">Data1!$P$124</definedName>
+    <definedName name="A2638790L">Data1!$BH$1:$BH$10,Data1!$BH$11:$BH$124</definedName>
+    <definedName name="A2638790L_Data">Data1!$BH$11:$BH$124</definedName>
+    <definedName name="A2638790L_Latest">Data1!$BH$124</definedName>
+    <definedName name="A2638791R">Data1!$CZ$1:$CZ$10,Data1!$CZ$11:$CZ$124</definedName>
+    <definedName name="A2638791R_Data">Data1!$CZ$11:$CZ$124</definedName>
+    <definedName name="A2638791R_Latest">Data1!$CZ$124</definedName>
+    <definedName name="A2638799J">Data1!$K$1:$K$10,Data1!$K$11:$K$124</definedName>
+    <definedName name="A2638799J_Data">Data1!$K$11:$K$124</definedName>
+    <definedName name="A2638799J_Latest">Data1!$K$124</definedName>
+    <definedName name="A2638800F">Data1!$BC$1:$BC$10,Data1!$BC$11:$BC$124</definedName>
+    <definedName name="A2638800F_Data">Data1!$BC$11:$BC$124</definedName>
+    <definedName name="A2638800F_Latest">Data1!$BC$124</definedName>
+    <definedName name="A2638801J">Data1!$CU$1:$CU$10,Data1!$CU$11:$CU$124</definedName>
+    <definedName name="A2638801J_Data">Data1!$CU$11:$CU$124</definedName>
+    <definedName name="A2638801J_Latest">Data1!$CU$124</definedName>
+    <definedName name="A2638809A">Data1!$I$1:$I$10,Data1!$I$11:$I$124</definedName>
+    <definedName name="A2638809A_Data">Data1!$I$11:$I$124</definedName>
+    <definedName name="A2638809A_Latest">Data1!$I$124</definedName>
+    <definedName name="A2638810K">Data1!$BA$1:$BA$10,Data1!$BA$11:$BA$124</definedName>
+    <definedName name="A2638810K_Data">Data1!$BA$11:$BA$124</definedName>
+    <definedName name="A2638810K_Latest">Data1!$BA$124</definedName>
+    <definedName name="A2638811L">Data1!$CS$1:$CS$10,Data1!$CS$11:$CS$124</definedName>
+    <definedName name="A2638811L_Data">Data1!$CS$11:$CS$124</definedName>
+    <definedName name="A2638811L_Latest">Data1!$CS$124</definedName>
+    <definedName name="A2638819F">Data1!$M$1:$M$10,Data1!$M$11:$M$124</definedName>
+    <definedName name="A2638819F_Data">Data1!$M$11:$M$124</definedName>
+    <definedName name="A2638819F_Latest">Data1!$M$124</definedName>
+    <definedName name="A2638820R">Data1!$BE$1:$BE$10,Data1!$BE$11:$BE$124</definedName>
+    <definedName name="A2638820R_Data">Data1!$BE$11:$BE$124</definedName>
+    <definedName name="A2638820R_Latest">Data1!$BE$124</definedName>
+    <definedName name="A2638821T">Data1!$CW$1:$CW$10,Data1!$CW$11:$CW$124</definedName>
+    <definedName name="A2638821T_Data">Data1!$CW$11:$CW$124</definedName>
+    <definedName name="A2638821T_Latest">Data1!$CW$124</definedName>
+    <definedName name="A2638829K">Data1!$D$1:$D$10,Data1!$D$11:$D$124</definedName>
+    <definedName name="A2638829K_Data">Data1!$D$11:$D$124</definedName>
+    <definedName name="A2638829K_Latest">Data1!$D$124</definedName>
+    <definedName name="A2638830V">Data1!$AV$1:$AV$10,Data1!$AV$11:$AV$124</definedName>
+    <definedName name="A2638830V_Data">Data1!$AV$11:$AV$124</definedName>
+    <definedName name="A2638830V_Latest">Data1!$AV$124</definedName>
+    <definedName name="A2638831W">Data1!$CN$1:$CN$10,Data1!$CN$11:$CN$124</definedName>
+    <definedName name="A2638831W_Data">Data1!$CN$11:$CN$124</definedName>
+    <definedName name="A2638831W_Latest">Data1!$CN$124</definedName>
+    <definedName name="A2638839R">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$124</definedName>
+    <definedName name="A2638839R_Data">Data1!$Q$11:$Q$124</definedName>
+    <definedName name="A2638839R_Latest">Data1!$Q$124</definedName>
+    <definedName name="A2638840X">Data1!$BI$1:$BI$10,Data1!$BI$11:$BI$124</definedName>
+    <definedName name="A2638840X_Data">Data1!$BI$11:$BI$124</definedName>
+    <definedName name="A2638840X_Latest">Data1!$BI$124</definedName>
+    <definedName name="A2638841A">Data1!$DA$1:$DA$10,Data1!$DA$11:$DA$124</definedName>
+    <definedName name="A2638841A_Data">Data1!$DA$11:$DA$124</definedName>
+    <definedName name="A2638841A_Latest">Data1!$DA$124</definedName>
+    <definedName name="A2638849V">Data1!$B$1:$B$10,Data1!$B$11:$B$124</definedName>
+    <definedName name="A2638849V_Data">Data1!$B$11:$B$124</definedName>
+    <definedName name="A2638849V_Latest">Data1!$B$124</definedName>
+    <definedName name="A2638850C">Data1!$AT$1:$AT$10,Data1!$AT$11:$AT$124</definedName>
+    <definedName name="A2638850C_Data">Data1!$AT$11:$AT$124</definedName>
+    <definedName name="A2638850C_Latest">Data1!$AT$124</definedName>
+    <definedName name="A2638851F">Data1!$CL$1:$CL$10,Data1!$CL$11:$CL$124</definedName>
+    <definedName name="A2638851F_Data">Data1!$CL$11:$CL$124</definedName>
+    <definedName name="A2638851F_Latest">Data1!$CL$124</definedName>
+    <definedName name="A2638859X">Data1!$J$1:$J$10,Data1!$J$11:$J$124</definedName>
+    <definedName name="A2638859X_Data">Data1!$J$11:$J$124</definedName>
+    <definedName name="A2638859X_Latest">Data1!$J$124</definedName>
+    <definedName name="A2638860J">Data1!$BB$1:$BB$10,Data1!$BB$11:$BB$124</definedName>
+    <definedName name="A2638860J_Data">Data1!$BB$11:$BB$124</definedName>
+    <definedName name="A2638860J_Latest">Data1!$BB$124</definedName>
+    <definedName name="A2638861K">Data1!$CT$1:$CT$10,Data1!$CT$11:$CT$124</definedName>
+    <definedName name="A2638861K_Data">Data1!$CT$11:$CT$124</definedName>
+    <definedName name="A2638861K_Latest">Data1!$CT$124</definedName>
+    <definedName name="A2638869C">Data1!$C$1:$C$10,Data1!$C$11:$C$124</definedName>
+    <definedName name="A2638869C_Data">Data1!$C$11:$C$124</definedName>
+    <definedName name="A2638869C_Latest">Data1!$C$124</definedName>
+    <definedName name="A2638870L">Data1!$AU$1:$AU$10,Data1!$AU$11:$AU$124</definedName>
+    <definedName name="A2638870L_Data">Data1!$AU$11:$AU$124</definedName>
+    <definedName name="A2638870L_Latest">Data1!$AU$124</definedName>
+    <definedName name="A2638871R">Data1!$CM$1:$CM$10,Data1!$CM$11:$CM$124</definedName>
+    <definedName name="A2638871R_Data">Data1!$CM$11:$CM$124</definedName>
+    <definedName name="A2638871R_Latest">Data1!$CM$124</definedName>
+    <definedName name="A2638879J">Data1!$N$1:$N$10,Data1!$N$11:$N$124</definedName>
+    <definedName name="A2638879J_Data">Data1!$N$11:$N$124</definedName>
+    <definedName name="A2638879J_Latest">Data1!$N$124</definedName>
+    <definedName name="A2638880T">Data1!$BF$1:$BF$10,Data1!$BF$11:$BF$124</definedName>
+    <definedName name="A2638880T_Data">Data1!$BF$11:$BF$124</definedName>
+    <definedName name="A2638880T_Latest">Data1!$BF$124</definedName>
+    <definedName name="A2638881V">Data1!$CX$1:$CX$10,Data1!$CX$11:$CX$124</definedName>
+    <definedName name="A2638881V_Data">Data1!$CX$11:$CX$124</definedName>
+    <definedName name="A2638881V_Latest">Data1!$CX$124</definedName>
+    <definedName name="A2638889L">Data1!$O$1:$O$10,Data1!$O$11:$O$124</definedName>
+    <definedName name="A2638889L_Data">Data1!$O$11:$O$124</definedName>
+    <definedName name="A2638889L_Latest">Data1!$O$124</definedName>
+    <definedName name="A2638890W">Data1!$BG$1:$BG$10,Data1!$BG$11:$BG$124</definedName>
+    <definedName name="A2638890W_Data">Data1!$BG$11:$BG$124</definedName>
+    <definedName name="A2638890W_Latest">Data1!$BG$124</definedName>
+    <definedName name="A2638891X">Data1!$CY$1:$CY$10,Data1!$CY$11:$CY$124</definedName>
+    <definedName name="A2638891X_Data">Data1!$CY$11:$CY$124</definedName>
+    <definedName name="A2638891X_Latest">Data1!$CY$124</definedName>
+    <definedName name="A2638899T">Data1!$G$1:$G$10,Data1!$G$11:$G$124</definedName>
+    <definedName name="A2638899T_Data">Data1!$G$11:$G$124</definedName>
+    <definedName name="A2638899T_Latest">Data1!$G$124</definedName>
+    <definedName name="A2638900R">Data1!$AY$1:$AY$10,Data1!$AY$11:$AY$124</definedName>
+    <definedName name="A2638900R_Data">Data1!$AY$11:$AY$124</definedName>
+    <definedName name="A2638900R_Latest">Data1!$AY$124</definedName>
+    <definedName name="A2638901T">Data1!$CQ$1:$CQ$10,Data1!$CQ$11:$CQ$124</definedName>
+    <definedName name="A2638901T_Data">Data1!$CQ$11:$CQ$124</definedName>
+    <definedName name="A2638901T_Latest">Data1!$CQ$124</definedName>
+    <definedName name="A2638909K">Data1!$F$1:$F$10,Data1!$F$11:$F$124</definedName>
+    <definedName name="A2638909K_Data">Data1!$F$11:$F$124</definedName>
+    <definedName name="A2638909K_Latest">Data1!$F$124</definedName>
+    <definedName name="A2638910V">Data1!$AX$1:$AX$10,Data1!$AX$11:$AX$124</definedName>
+    <definedName name="A2638910V_Data">Data1!$AX$11:$AX$124</definedName>
+    <definedName name="A2638910V_Latest">Data1!$AX$124</definedName>
+    <definedName name="A2638911W">Data1!$CP$1:$CP$10,Data1!$CP$11:$CP$124</definedName>
+    <definedName name="A2638911W_Data">Data1!$CP$11:$CP$124</definedName>
+    <definedName name="A2638911W_Latest">Data1!$CP$124</definedName>
+    <definedName name="A2638919R">Data1!$S$1:$S$10,Data1!$S$11:$S$124</definedName>
+    <definedName name="A2638919R_Data">Data1!$S$11:$S$124</definedName>
+    <definedName name="A2638919R_Latest">Data1!$S$124</definedName>
+    <definedName name="A2638920X">Data1!$BK$1:$BK$10,Data1!$BK$11:$BK$124</definedName>
+    <definedName name="A2638920X_Data">Data1!$BK$11:$BK$124</definedName>
+    <definedName name="A2638920X_Latest">Data1!$BK$124</definedName>
+    <definedName name="A2638921A">Data1!$DC$1:$DC$10,Data1!$DC$11:$DC$124</definedName>
+    <definedName name="A2638921A_Data">Data1!$DC$11:$DC$124</definedName>
+    <definedName name="A2638921A_Latest">Data1!$DC$124</definedName>
+    <definedName name="A2638929V">Data1!$E$1:$E$10,Data1!$E$11:$E$124</definedName>
+    <definedName name="A2638929V_Data">Data1!$E$11:$E$124</definedName>
+    <definedName name="A2638929V_Latest">Data1!$E$124</definedName>
+    <definedName name="A2638930C">Data1!$AW$1:$AW$10,Data1!$AW$11:$AW$124</definedName>
+    <definedName name="A2638930C_Data">Data1!$AW$11:$AW$124</definedName>
+    <definedName name="A2638930C_Latest">Data1!$AW$124</definedName>
+    <definedName name="A2638931F">Data1!$CO$1:$CO$10,Data1!$CO$11:$CO$124</definedName>
+    <definedName name="A2638931F_Data">Data1!$CO$11:$CO$124</definedName>
+    <definedName name="A2638931F_Latest">Data1!$CO$124</definedName>
+    <definedName name="A2638939X">Data1!$L$1:$L$10,Data1!$L$11:$L$124</definedName>
+    <definedName name="A2638939X_Data">Data1!$L$11:$L$124</definedName>
+    <definedName name="A2638939X_Latest">Data1!$L$124</definedName>
+    <definedName name="A2638940J">Data1!$BD$1:$BD$10,Data1!$BD$11:$BD$124</definedName>
+    <definedName name="A2638940J_Data">Data1!$BD$11:$BD$124</definedName>
+    <definedName name="A2638940J_Latest">Data1!$BD$124</definedName>
+    <definedName name="A2638941K">Data1!$CV$1:$CV$10,Data1!$CV$11:$CV$124</definedName>
+    <definedName name="A2638941K_Data">Data1!$CV$11:$CV$124</definedName>
+    <definedName name="A2638941K_Latest">Data1!$CV$124</definedName>
+    <definedName name="A2638949C">Data1!$T$1:$T$10,Data1!$T$11:$T$124</definedName>
+    <definedName name="A2638949C_Data">Data1!$T$11:$T$124</definedName>
+    <definedName name="A2638949C_Latest">Data1!$T$124</definedName>
+    <definedName name="A2638950L">Data1!$BL$1:$BL$10,Data1!$BL$11:$BL$124</definedName>
+    <definedName name="A2638950L_Data">Data1!$BL$11:$BL$124</definedName>
+    <definedName name="A2638950L_Latest">Data1!$BL$124</definedName>
+    <definedName name="A2638951R">Data1!$DD$1:$DD$10,Data1!$DD$11:$DD$124</definedName>
+    <definedName name="A2638951R_Data">Data1!$DD$11:$DD$124</definedName>
+    <definedName name="A2638951R_Latest">Data1!$DD$124</definedName>
+    <definedName name="A2639339L">Data1!$AQ$1:$AQ$10,Data1!$AQ$11:$AQ$124</definedName>
+    <definedName name="A2639339L_Data">Data1!$AQ$11:$AQ$124</definedName>
+    <definedName name="A2639339L_Latest">Data1!$AQ$124</definedName>
+    <definedName name="A2639340W">Data1!$CI$1:$CI$10,Data1!$CI$11:$CI$124</definedName>
+    <definedName name="A2639340W_Data">Data1!$CI$11:$CI$124</definedName>
+    <definedName name="A2639340W_Latest">Data1!$CI$124</definedName>
+    <definedName name="A2639341X">Data1!$EA$1:$EA$10,Data1!$EA$11:$EA$124</definedName>
+    <definedName name="A2639341X_Data">Data1!$EA$11:$EA$124</definedName>
+    <definedName name="A2639341X_Latest">Data1!$EA$124</definedName>
+    <definedName name="A2639349T">Data1!$AG$1:$AG$10,Data1!$AG$11:$AG$124</definedName>
+    <definedName name="A2639349T_Data">Data1!$AG$11:$AG$124</definedName>
+    <definedName name="A2639349T_Latest">Data1!$AG$124</definedName>
+    <definedName name="A2639350A">Data1!$BY$1:$BY$10,Data1!$BY$11:$BY$124</definedName>
+    <definedName name="A2639350A_Data">Data1!$BY$11:$BY$124</definedName>
+    <definedName name="A2639350A_Latest">Data1!$BY$124</definedName>
+    <definedName name="A2639351C">Data1!$DQ$1:$DQ$10,Data1!$DQ$11:$DQ$124</definedName>
+    <definedName name="A2639351C_Data">Data1!$DQ$11:$DQ$124</definedName>
+    <definedName name="A2639351C_Latest">Data1!$DQ$124</definedName>
+    <definedName name="A2639359W">Data1!$AO$1:$AO$10,Data1!$AO$11:$AO$124</definedName>
+    <definedName name="A2639359W_Data">Data1!$AO$11:$AO$124</definedName>
+    <definedName name="A2639359W_Latest">Data1!$AO$124</definedName>
+    <definedName name="A2639360F">Data1!$CG$1:$CG$10,Data1!$CG$11:$CG$124</definedName>
+    <definedName name="A2639360F_Data">Data1!$CG$11:$CG$124</definedName>
+    <definedName name="A2639360F_Latest">Data1!$CG$124</definedName>
+    <definedName name="A2639361J">Data1!$DY$1:$DY$10,Data1!$DY$11:$DY$124</definedName>
+    <definedName name="A2639361J_Data">Data1!$DY$11:$DY$124</definedName>
+    <definedName name="A2639361J_Latest">Data1!$DY$124</definedName>
+    <definedName name="A2639369A">Data1!$AJ$1:$AJ$10,Data1!$AJ$11:$AJ$124</definedName>
+    <definedName name="A2639369A_Data">Data1!$AJ$11:$AJ$124</definedName>
+    <definedName name="A2639369A_Latest">Data1!$AJ$124</definedName>
+    <definedName name="A2639370K">Data1!$CB$1:$CB$10,Data1!$CB$11:$CB$124</definedName>
+    <definedName name="A2639370K_Data">Data1!$CB$11:$CB$124</definedName>
+    <definedName name="A2639370K_Latest">Data1!$CB$124</definedName>
+    <definedName name="A2639371L">Data1!$DT$1:$DT$10,Data1!$DT$11:$DT$124</definedName>
+    <definedName name="A2639371L_Data">Data1!$DT$11:$DT$124</definedName>
+    <definedName name="A2639371L_Latest">Data1!$DT$124</definedName>
+    <definedName name="A2639379F">Data1!$AH$1:$AH$10,Data1!$AH$11:$AH$124</definedName>
+    <definedName name="A2639379F_Data">Data1!$AH$11:$AH$124</definedName>
+    <definedName name="A2639379F_Latest">Data1!$AH$124</definedName>
+    <definedName name="A2639380R">Data1!$BZ$1:$BZ$10,Data1!$BZ$11:$BZ$124</definedName>
+    <definedName name="A2639380R_Data">Data1!$BZ$11:$BZ$124</definedName>
+    <definedName name="A2639380R_Latest">Data1!$BZ$124</definedName>
+    <definedName name="A2639381T">Data1!$DR$1:$DR$10,Data1!$DR$11:$DR$124</definedName>
+    <definedName name="A2639381T_Data">Data1!$DR$11:$DR$124</definedName>
+    <definedName name="A2639381T_Latest">Data1!$DR$124</definedName>
+    <definedName name="A2639389K">Data1!$AL$1:$AL$10,Data1!$AL$11:$AL$124</definedName>
+    <definedName name="A2639389K_Data">Data1!$AL$11:$AL$124</definedName>
+    <definedName name="A2639389K_Latest">Data1!$AL$124</definedName>
+    <definedName name="A2639390V">Data1!$CD$1:$CD$10,Data1!$CD$11:$CD$124</definedName>
+    <definedName name="A2639390V_Data">Data1!$CD$11:$CD$124</definedName>
+    <definedName name="A2639390V_Latest">Data1!$CD$124</definedName>
+    <definedName name="A2639391W">Data1!$DV$1:$DV$10,Data1!$DV$11:$DV$124</definedName>
+    <definedName name="A2639391W_Data">Data1!$DV$11:$DV$124</definedName>
+    <definedName name="A2639391W_Latest">Data1!$DV$124</definedName>
+    <definedName name="A2639399R">Data1!$AC$1:$AC$10,Data1!$AC$11:$AC$124</definedName>
+    <definedName name="A2639399R_Data">Data1!$AC$11:$AC$124</definedName>
+    <definedName name="A2639399R_Latest">Data1!$AC$124</definedName>
+    <definedName name="A2639400L">Data1!$BU$1:$BU$10,Data1!$BU$11:$BU$124</definedName>
+    <definedName name="A2639400L_Data">Data1!$BU$11:$BU$124</definedName>
+    <definedName name="A2639400L_Latest">Data1!$BU$124</definedName>
+    <definedName name="A2639401R">Data1!$DM$1:$DM$10,Data1!$DM$11:$DM$124</definedName>
+    <definedName name="A2639401R_Data">Data1!$DM$11:$DM$124</definedName>
+    <definedName name="A2639401R_Latest">Data1!$DM$124</definedName>
+    <definedName name="A2639409J">Data1!$AP$1:$AP$10,Data1!$AP$11:$AP$124</definedName>
+    <definedName name="A2639409J_Data">Data1!$AP$11:$AP$124</definedName>
+    <definedName name="A2639409J_Latest">Data1!$AP$124</definedName>
+    <definedName name="A2639410T">Data1!$CH$1:$CH$10,Data1!$CH$11:$CH$124</definedName>
+    <definedName name="A2639410T_Data">Data1!$CH$11:$CH$124</definedName>
+    <definedName name="A2639410T_Latest">Data1!$CH$124</definedName>
+    <definedName name="A2639411V">Data1!$DZ$1:$DZ$10,Data1!$DZ$11:$DZ$124</definedName>
+    <definedName name="A2639411V_Data">Data1!$DZ$11:$DZ$124</definedName>
+    <definedName name="A2639411V_Latest">Data1!$DZ$124</definedName>
+    <definedName name="A2639419L">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$124</definedName>
+    <definedName name="A2639419L_Data">Data1!$AA$11:$AA$124</definedName>
+    <definedName name="A2639419L_Latest">Data1!$AA$124</definedName>
+    <definedName name="A2639420W">Data1!$BS$1:$BS$10,Data1!$BS$11:$BS$124</definedName>
+    <definedName name="A2639420W_Data">Data1!$BS$11:$BS$124</definedName>
+    <definedName name="A2639420W_Latest">Data1!$BS$124</definedName>
+    <definedName name="A2639421X">Data1!$DK$1:$DK$10,Data1!$DK$11:$DK$124</definedName>
+    <definedName name="A2639421X_Data">Data1!$DK$11:$DK$124</definedName>
+    <definedName name="A2639421X_Latest">Data1!$DK$124</definedName>
+    <definedName name="A2639429T">Data1!$AI$1:$AI$10,Data1!$AI$11:$AI$124</definedName>
+    <definedName name="A2639429T_Data">Data1!$AI$11:$AI$124</definedName>
+    <definedName name="A2639429T_Latest">Data1!$AI$124</definedName>
+    <definedName name="A2639430A">Data1!$CA$1:$CA$10,Data1!$CA$11:$CA$124</definedName>
+    <definedName name="A2639430A_Data">Data1!$CA$11:$CA$124</definedName>
+    <definedName name="A2639430A_Latest">Data1!$CA$124</definedName>
+    <definedName name="A2639431C">Data1!$DS$1:$DS$10,Data1!$DS$11:$DS$124</definedName>
+    <definedName name="A2639431C_Data">Data1!$DS$11:$DS$124</definedName>
+    <definedName name="A2639431C_Latest">Data1!$DS$124</definedName>
+    <definedName name="A2639439W">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$124</definedName>
+    <definedName name="A2639439W_Data">Data1!$AB$11:$AB$124</definedName>
+    <definedName name="A2639439W_Latest">Data1!$AB$124</definedName>
+    <definedName name="A2639440F">Data1!$BT$1:$BT$10,Data1!$BT$11:$BT$124</definedName>
+    <definedName name="A2639440F_Data">Data1!$BT$11:$BT$124</definedName>
+    <definedName name="A2639440F_Latest">Data1!$BT$124</definedName>
+    <definedName name="A2639441J">Data1!$DL$1:$DL$10,Data1!$DL$11:$DL$124</definedName>
+    <definedName name="A2639441J_Data">Data1!$DL$11:$DL$124</definedName>
+    <definedName name="A2639441J_Latest">Data1!$DL$124</definedName>
+    <definedName name="A2639449A">Data1!$AM$1:$AM$10,Data1!$AM$11:$AM$124</definedName>
+    <definedName name="A2639449A_Data">Data1!$AM$11:$AM$124</definedName>
+    <definedName name="A2639449A_Latest">Data1!$AM$124</definedName>
+    <definedName name="A2639450K">Data1!$CE$1:$CE$10,Data1!$CE$11:$CE$124</definedName>
+    <definedName name="A2639450K_Data">Data1!$CE$11:$CE$124</definedName>
+    <definedName name="A2639450K_Latest">Data1!$CE$124</definedName>
+    <definedName name="A2639451L">Data1!$DW$1:$DW$10,Data1!$DW$11:$DW$124</definedName>
+    <definedName name="A2639451L_Data">Data1!$DW$11:$DW$124</definedName>
+    <definedName name="A2639451L_Latest">Data1!$DW$124</definedName>
+    <definedName name="A2639459F">Data1!$AN$1:$AN$10,Data1!$AN$11:$AN$124</definedName>
+    <definedName name="A2639459F_Data">Data1!$AN$11:$AN$124</definedName>
+    <definedName name="A2639459F_Latest">Data1!$AN$124</definedName>
+    <definedName name="A2639460R">Data1!$CF$1:$CF$10,Data1!$CF$11:$CF$124</definedName>
+    <definedName name="A2639460R_Data">Data1!$CF$11:$CF$124</definedName>
+    <definedName name="A2639460R_Latest">Data1!$CF$124</definedName>
+    <definedName name="A2639461T">Data1!$DX$1:$DX$10,Data1!$DX$11:$DX$124</definedName>
+    <definedName name="A2639461T_Data">Data1!$DX$11:$DX$124</definedName>
+    <definedName name="A2639461T_Latest">Data1!$DX$124</definedName>
+    <definedName name="A2639469K">Data1!$AF$1:$AF$10,Data1!$AF$11:$AF$124</definedName>
+    <definedName name="A2639469K_Data">Data1!$AF$11:$AF$124</definedName>
+    <definedName name="A2639469K_Latest">Data1!$AF$124</definedName>
+    <definedName name="A2639470V">Data1!$BX$1:$BX$10,Data1!$BX$11:$BX$124</definedName>
+    <definedName name="A2639470V_Data">Data1!$BX$11:$BX$124</definedName>
+    <definedName name="A2639470V_Latest">Data1!$BX$124</definedName>
+    <definedName name="A2639471W">Data1!$DP$1:$DP$10,Data1!$DP$11:$DP$124</definedName>
+    <definedName name="A2639471W_Data">Data1!$DP$11:$DP$124</definedName>
+    <definedName name="A2639471W_Latest">Data1!$DP$124</definedName>
+    <definedName name="A2639479R">Data1!$AE$1:$AE$10,Data1!$AE$11:$AE$124</definedName>
+    <definedName name="A2639479R_Data">Data1!$AE$11:$AE$124</definedName>
+    <definedName name="A2639479R_Latest">Data1!$AE$124</definedName>
+    <definedName name="A2639480X">Data1!$BW$1:$BW$10,Data1!$BW$11:$BW$124</definedName>
+    <definedName name="A2639480X_Data">Data1!$BW$11:$BW$124</definedName>
+    <definedName name="A2639480X_Latest">Data1!$BW$124</definedName>
+    <definedName name="A2639481A">Data1!$DO$1:$DO$10,Data1!$DO$11:$DO$124</definedName>
+    <definedName name="A2639481A_Data">Data1!$DO$11:$DO$124</definedName>
+    <definedName name="A2639481A_Latest">Data1!$DO$124</definedName>
+    <definedName name="A2639489V">Data1!$AR$1:$AR$10,Data1!$AR$11:$AR$124</definedName>
+    <definedName name="A2639489V_Data">Data1!$AR$11:$AR$124</definedName>
+    <definedName name="A2639489V_Latest">Data1!$AR$124</definedName>
+    <definedName name="A2639490C">Data1!$CJ$1:$CJ$10,Data1!$CJ$11:$CJ$124</definedName>
+    <definedName name="A2639490C_Data">Data1!$CJ$11:$CJ$124</definedName>
+    <definedName name="A2639490C_Latest">Data1!$CJ$124</definedName>
+    <definedName name="A2639491F">Data1!$EB$1:$EB$10,Data1!$EB$11:$EB$124</definedName>
+    <definedName name="A2639491F_Data">Data1!$EB$11:$EB$124</definedName>
+    <definedName name="A2639491F_Latest">Data1!$EB$124</definedName>
+    <definedName name="A2639499X">Data1!$AD$1:$AD$10,Data1!$AD$11:$AD$124</definedName>
+    <definedName name="A2639499X_Data">Data1!$AD$11:$AD$124</definedName>
+    <definedName name="A2639499X_Latest">Data1!$AD$124</definedName>
+    <definedName name="A2639500W">Data1!$BV$1:$BV$10,Data1!$BV$11:$BV$124</definedName>
+    <definedName name="A2639500W_Data">Data1!$BV$11:$BV$124</definedName>
+    <definedName name="A2639500W_Latest">Data1!$BV$124</definedName>
+    <definedName name="A2639501X">Data1!$DN$1:$DN$10,Data1!$DN$11:$DN$124</definedName>
+    <definedName name="A2639501X_Data">Data1!$DN$11:$DN$124</definedName>
+    <definedName name="A2639501X_Latest">Data1!$DN$124</definedName>
+    <definedName name="A2639509T">Data1!$AK$1:$AK$10,Data1!$AK$11:$AK$124</definedName>
+    <definedName name="A2639509T_Data">Data1!$AK$11:$AK$124</definedName>
+    <definedName name="A2639509T_Latest">Data1!$AK$124</definedName>
+    <definedName name="A2639510A">Data1!$CC$1:$CC$10,Data1!$CC$11:$CC$124</definedName>
+    <definedName name="A2639510A_Data">Data1!$CC$11:$CC$124</definedName>
+    <definedName name="A2639510A_Latest">Data1!$CC$124</definedName>
+    <definedName name="A2639511C">Data1!$DU$1:$DU$10,Data1!$DU$11:$DU$124</definedName>
+    <definedName name="A2639511C_Data">Data1!$DU$11:$DU$124</definedName>
+    <definedName name="A2639511C_Latest">Data1!$DU$124</definedName>
+    <definedName name="A2639519W">Data1!$AS$1:$AS$10,Data1!$AS$11:$AS$124</definedName>
+    <definedName name="A2639519W_Data">Data1!$AS$11:$AS$124</definedName>
+    <definedName name="A2639519W_Latest">Data1!$AS$124</definedName>
+    <definedName name="A2639520F">Data1!$CK$1:$CK$10,Data1!$CK$11:$CK$124</definedName>
+    <definedName name="A2639520F_Data">Data1!$CK$11:$CK$124</definedName>
+    <definedName name="A2639520F_Latest">Data1!$CK$124</definedName>
+    <definedName name="A2639521J">Data1!$EC$1:$EC$10,Data1!$EC$11:$EC$124</definedName>
+    <definedName name="A2639521J_Data">Data1!$EC$11:$EC$124</definedName>
+    <definedName name="A2639521J_Latest">Data1!$EC$124</definedName>
+    <definedName name="A2639739X">Data1!$X$1:$X$10,Data1!$X$11:$X$124</definedName>
+    <definedName name="A2639739X_Data">Data1!$X$11:$X$124</definedName>
+    <definedName name="A2639739X_Latest">Data1!$X$124</definedName>
+    <definedName name="A2639740J">Data1!$BP$1:$BP$10,Data1!$BP$11:$BP$124</definedName>
+    <definedName name="A2639740J_Data">Data1!$BP$11:$BP$124</definedName>
+    <definedName name="A2639740J_Latest">Data1!$BP$124</definedName>
+    <definedName name="A2639741K">Data1!$DH$1:$DH$10,Data1!$DH$11:$DH$124</definedName>
+    <definedName name="A2639741K_Data">Data1!$DH$11:$DH$124</definedName>
+    <definedName name="A2639741K_Latest">Data1!$DH$124</definedName>
+    <definedName name="A2639769L">Data1!$V$1:$V$10,Data1!$V$11:$V$124</definedName>
+    <definedName name="A2639769L_Data">Data1!$V$11:$V$124</definedName>
+    <definedName name="A2639769L_Latest">Data1!$V$124</definedName>
+    <definedName name="A2639770W">Data1!$BN$1:$BN$10,Data1!$BN$11:$BN$124</definedName>
+    <definedName name="A2639770W_Data">Data1!$BN$11:$BN$124</definedName>
+    <definedName name="A2639770W_Latest">Data1!$BN$124</definedName>
+    <definedName name="A2639771X">Data1!$DF$1:$DF$10,Data1!$DF$11:$DF$124</definedName>
+    <definedName name="A2639771X_Data">Data1!$DF$11:$DF$124</definedName>
+    <definedName name="A2639771X_Latest">Data1!$DF$124</definedName>
+    <definedName name="A2639779T">Data1!$U$1:$U$10,Data1!$U$11:$U$124</definedName>
+    <definedName name="A2639779T_Data">Data1!$U$11:$U$124</definedName>
+    <definedName name="A2639779T_Latest">Data1!$U$124</definedName>
+    <definedName name="A2639780A">Data1!$BM$1:$BM$10,Data1!$BM$11:$BM$124</definedName>
+    <definedName name="A2639780A_Data">Data1!$BM$11:$BM$124</definedName>
+    <definedName name="A2639780A_Latest">Data1!$BM$124</definedName>
+    <definedName name="A2639781C">Data1!$DE$1:$DE$10,Data1!$DE$11:$DE$124</definedName>
+    <definedName name="A2639781C_Data">Data1!$DE$11:$DE$124</definedName>
+    <definedName name="A2639781C_Latest">Data1!$DE$124</definedName>
+    <definedName name="A2639789W">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$124</definedName>
+    <definedName name="A2639789W_Data">Data1!$Y$11:$Y$124</definedName>
+    <definedName name="A2639789W_Latest">Data1!$Y$124</definedName>
+    <definedName name="A2639790F">Data1!$BQ$1:$BQ$10,Data1!$BQ$11:$BQ$124</definedName>
+    <definedName name="A2639790F_Data">Data1!$BQ$11:$BQ$124</definedName>
+    <definedName name="A2639790F_Latest">Data1!$BQ$124</definedName>
+    <definedName name="A2639791J">Data1!$DI$1:$DI$10,Data1!$DI$11:$DI$124</definedName>
+    <definedName name="A2639791J_Data">Data1!$DI$11:$DI$124</definedName>
+    <definedName name="A2639791J_Latest">Data1!$DI$124</definedName>
+    <definedName name="A2639839J">Data1!$W$1:$W$10,Data1!$W$11:$W$124</definedName>
+    <definedName name="A2639839J_Data">Data1!$W$11:$W$124</definedName>
+    <definedName name="A2639839J_Latest">Data1!$W$124</definedName>
+    <definedName name="A2639840T">Data1!$BO$1:$BO$10,Data1!$BO$11:$BO$124</definedName>
+    <definedName name="A2639840T_Data">Data1!$BO$11:$BO$124</definedName>
+    <definedName name="A2639840T_Latest">Data1!$BO$124</definedName>
+    <definedName name="A2639841V">Data1!$DG$1:$DG$10,Data1!$DG$11:$DG$124</definedName>
+    <definedName name="A2639841V_Data">Data1!$DG$11:$DG$124</definedName>
+    <definedName name="A2639841V_Latest">Data1!$DG$124</definedName>
+    <definedName name="A2639899K">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$124</definedName>
+    <definedName name="A2639899K_Data">Data1!$Z$11:$Z$124</definedName>
+    <definedName name="A2639899K_Latest">Data1!$Z$124</definedName>
+    <definedName name="A2639900J">Data1!$BR$1:$BR$10,Data1!$BR$11:$BR$124</definedName>
+    <definedName name="A2639900J_Data">Data1!$BR$11:$BR$124</definedName>
+    <definedName name="A2639900J_Latest">Data1!$BR$124</definedName>
+    <definedName name="A2639901K">Data1!$DJ$1:$DJ$10,Data1!$DJ$11:$DJ$124</definedName>
+    <definedName name="A2639901K_Data">Data1!$DJ$11:$DJ$124</definedName>
+    <definedName name="A2639901K_Latest">Data1!$DJ$124</definedName>
+    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$124</definedName>
+    <definedName name="Date_Range_Data">Data1!$A$11:$A$124</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -7632,7 +7632,7 @@
     <t>Freq.</t>
   </si>
   <si>
-    <t>© Commonwealth of Australia  2023</t>
+    <t>© Commonwealth of Australia  2026</t>
   </si>
 </sst>
 </file>
@@ -8313,10 +8313,10 @@
         <v>35674</v>
       </c>
       <c r="G12" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H12" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>141</v>
@@ -8345,10 +8345,10 @@
         <v>35674</v>
       </c>
       <c r="G13" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H13" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>141</v>
@@ -8377,10 +8377,10 @@
         <v>35674</v>
       </c>
       <c r="G14" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H14" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>141</v>
@@ -8409,10 +8409,10 @@
         <v>35674</v>
       </c>
       <c r="G15" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H15" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>141</v>
@@ -8441,10 +8441,10 @@
         <v>35674</v>
       </c>
       <c r="G16" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H16" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>141</v>
@@ -8473,10 +8473,10 @@
         <v>35674</v>
       </c>
       <c r="G17" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H17" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>141</v>
@@ -8505,10 +8505,10 @@
         <v>35674</v>
       </c>
       <c r="G18" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H18" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>141</v>
@@ -8537,10 +8537,10 @@
         <v>35674</v>
       </c>
       <c r="G19" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H19" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>141</v>
@@ -8569,10 +8569,10 @@
         <v>35674</v>
       </c>
       <c r="G20" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H20" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>141</v>
@@ -8601,10 +8601,10 @@
         <v>35674</v>
       </c>
       <c r="G21" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H21" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>141</v>
@@ -8633,10 +8633,10 @@
         <v>35674</v>
       </c>
       <c r="G22" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H22" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>141</v>
@@ -8665,10 +8665,10 @@
         <v>35674</v>
       </c>
       <c r="G23" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H23" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>141</v>
@@ -8697,10 +8697,10 @@
         <v>35674</v>
       </c>
       <c r="G24" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H24" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>141</v>
@@ -8729,10 +8729,10 @@
         <v>35674</v>
       </c>
       <c r="G25" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H25" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>141</v>
@@ -8761,10 +8761,10 @@
         <v>35674</v>
       </c>
       <c r="G26" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H26" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>141</v>
@@ -8793,10 +8793,10 @@
         <v>35674</v>
       </c>
       <c r="G27" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H27" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>141</v>
@@ -8825,10 +8825,10 @@
         <v>35674</v>
       </c>
       <c r="G28" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H28" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>141</v>
@@ -8857,10 +8857,10 @@
         <v>35674</v>
       </c>
       <c r="G29" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H29" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>141</v>
@@ -8889,10 +8889,10 @@
         <v>35674</v>
       </c>
       <c r="G30" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H30" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I30" s="10" t="s">
         <v>141</v>
@@ -8921,10 +8921,10 @@
         <v>35674</v>
       </c>
       <c r="G31" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H31" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I31" s="10" t="s">
         <v>141</v>
@@ -8953,10 +8953,10 @@
         <v>35674</v>
       </c>
       <c r="G32" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H32" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>141</v>
@@ -8985,10 +8985,10 @@
         <v>35674</v>
       </c>
       <c r="G33" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H33" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I33" s="10" t="s">
         <v>141</v>
@@ -9017,10 +9017,10 @@
         <v>35674</v>
       </c>
       <c r="G34" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H34" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I34" s="10" t="s">
         <v>141</v>
@@ -9049,10 +9049,10 @@
         <v>35674</v>
       </c>
       <c r="G35" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H35" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>141</v>
@@ -9081,10 +9081,10 @@
         <v>35674</v>
       </c>
       <c r="G36" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H36" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I36" s="10" t="s">
         <v>141</v>
@@ -9113,10 +9113,10 @@
         <v>35674</v>
       </c>
       <c r="G37" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H37" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I37" s="10" t="s">
         <v>141</v>
@@ -9145,10 +9145,10 @@
         <v>35674</v>
       </c>
       <c r="G38" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H38" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I38" s="10" t="s">
         <v>141</v>
@@ -9177,10 +9177,10 @@
         <v>35674</v>
       </c>
       <c r="G39" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H39" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I39" s="10" t="s">
         <v>141</v>
@@ -9209,10 +9209,10 @@
         <v>35674</v>
       </c>
       <c r="G40" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H40" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I40" s="10" t="s">
         <v>141</v>
@@ -9241,10 +9241,10 @@
         <v>35674</v>
       </c>
       <c r="G41" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H41" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I41" s="10" t="s">
         <v>141</v>
@@ -9273,10 +9273,10 @@
         <v>35674</v>
       </c>
       <c r="G42" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H42" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I42" s="10" t="s">
         <v>141</v>
@@ -9305,10 +9305,10 @@
         <v>35674</v>
       </c>
       <c r="G43" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H43" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I43" s="10" t="s">
         <v>141</v>
@@ -9337,10 +9337,10 @@
         <v>35674</v>
       </c>
       <c r="G44" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H44" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I44" s="10" t="s">
         <v>141</v>
@@ -9369,10 +9369,10 @@
         <v>35674</v>
       </c>
       <c r="G45" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H45" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I45" s="10" t="s">
         <v>141</v>
@@ -9401,10 +9401,10 @@
         <v>35674</v>
       </c>
       <c r="G46" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H46" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I46" s="10" t="s">
         <v>141</v>
@@ -9433,10 +9433,10 @@
         <v>35674</v>
       </c>
       <c r="G47" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H47" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I47" s="10" t="s">
         <v>141</v>
@@ -9465,10 +9465,10 @@
         <v>35674</v>
       </c>
       <c r="G48" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H48" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I48" s="10" t="s">
         <v>141</v>
@@ -9497,10 +9497,10 @@
         <v>35674</v>
       </c>
       <c r="G49" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H49" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I49" s="10" t="s">
         <v>141</v>
@@ -9529,10 +9529,10 @@
         <v>35674</v>
       </c>
       <c r="G50" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H50" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I50" s="10" t="s">
         <v>141</v>
@@ -9561,10 +9561,10 @@
         <v>35674</v>
       </c>
       <c r="G51" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H51" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I51" s="10" t="s">
         <v>141</v>
@@ -9593,10 +9593,10 @@
         <v>35674</v>
       </c>
       <c r="G52" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H52" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I52" s="10" t="s">
         <v>141</v>
@@ -9625,10 +9625,10 @@
         <v>35674</v>
       </c>
       <c r="G53" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H53" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I53" s="10" t="s">
         <v>141</v>
@@ -9657,10 +9657,10 @@
         <v>35674</v>
       </c>
       <c r="G54" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H54" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I54" s="10" t="s">
         <v>141</v>
@@ -9689,10 +9689,10 @@
         <v>35674</v>
       </c>
       <c r="G55" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H55" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I55" s="10" t="s">
         <v>141</v>
@@ -9721,10 +9721,10 @@
         <v>35674</v>
       </c>
       <c r="G56" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H56" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I56" s="10" t="s">
         <v>189</v>
@@ -9753,10 +9753,10 @@
         <v>35674</v>
       </c>
       <c r="G57" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H57" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I57" s="10" t="s">
         <v>189</v>
@@ -9785,10 +9785,10 @@
         <v>35674</v>
       </c>
       <c r="G58" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H58" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I58" s="10" t="s">
         <v>189</v>
@@ -9817,10 +9817,10 @@
         <v>35674</v>
       </c>
       <c r="G59" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H59" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I59" s="10" t="s">
         <v>189</v>
@@ -9849,10 +9849,10 @@
         <v>35674</v>
       </c>
       <c r="G60" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H60" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I60" s="10" t="s">
         <v>189</v>
@@ -9881,10 +9881,10 @@
         <v>35674</v>
       </c>
       <c r="G61" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H61" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I61" s="10" t="s">
         <v>189</v>
@@ -9913,10 +9913,10 @@
         <v>35674</v>
       </c>
       <c r="G62" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H62" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I62" s="10" t="s">
         <v>189</v>
@@ -9945,10 +9945,10 @@
         <v>35674</v>
       </c>
       <c r="G63" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H63" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I63" s="10" t="s">
         <v>189</v>
@@ -9977,10 +9977,10 @@
         <v>35674</v>
       </c>
       <c r="G64" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H64" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I64" s="10" t="s">
         <v>189</v>
@@ -10009,10 +10009,10 @@
         <v>35674</v>
       </c>
       <c r="G65" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H65" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I65" s="10" t="s">
         <v>189</v>
@@ -10041,10 +10041,10 @@
         <v>35674</v>
       </c>
       <c r="G66" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H66" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I66" s="10" t="s">
         <v>189</v>
@@ -10073,10 +10073,10 @@
         <v>35674</v>
       </c>
       <c r="G67" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H67" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I67" s="10" t="s">
         <v>189</v>
@@ -10105,10 +10105,10 @@
         <v>35674</v>
       </c>
       <c r="G68" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H68" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I68" s="10" t="s">
         <v>189</v>
@@ -10137,10 +10137,10 @@
         <v>35674</v>
       </c>
       <c r="G69" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H69" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I69" s="10" t="s">
         <v>189</v>
@@ -10169,10 +10169,10 @@
         <v>35674</v>
       </c>
       <c r="G70" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H70" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I70" s="10" t="s">
         <v>189</v>
@@ -10201,10 +10201,10 @@
         <v>35674</v>
       </c>
       <c r="G71" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H71" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I71" s="10" t="s">
         <v>189</v>
@@ -10233,10 +10233,10 @@
         <v>35674</v>
       </c>
       <c r="G72" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H72" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I72" s="10" t="s">
         <v>189</v>
@@ -10265,10 +10265,10 @@
         <v>35674</v>
       </c>
       <c r="G73" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H73" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I73" s="10" t="s">
         <v>189</v>
@@ -10297,10 +10297,10 @@
         <v>35674</v>
       </c>
       <c r="G74" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H74" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I74" s="10" t="s">
         <v>189</v>
@@ -10329,10 +10329,10 @@
         <v>35674</v>
       </c>
       <c r="G75" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H75" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I75" s="10" t="s">
         <v>189</v>
@@ -10361,10 +10361,10 @@
         <v>35674</v>
       </c>
       <c r="G76" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H76" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I76" s="10" t="s">
         <v>189</v>
@@ -10393,10 +10393,10 @@
         <v>35674</v>
       </c>
       <c r="G77" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H77" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I77" s="10" t="s">
         <v>189</v>
@@ -10425,10 +10425,10 @@
         <v>35674</v>
       </c>
       <c r="G78" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H78" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I78" s="10" t="s">
         <v>189</v>
@@ -10457,10 +10457,10 @@
         <v>35674</v>
       </c>
       <c r="G79" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H79" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I79" s="10" t="s">
         <v>189</v>
@@ -10489,10 +10489,10 @@
         <v>35674</v>
       </c>
       <c r="G80" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H80" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I80" s="10" t="s">
         <v>189</v>
@@ -10521,10 +10521,10 @@
         <v>35674</v>
       </c>
       <c r="G81" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H81" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I81" s="10" t="s">
         <v>189</v>
@@ -10553,10 +10553,10 @@
         <v>35674</v>
       </c>
       <c r="G82" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H82" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I82" s="10" t="s">
         <v>189</v>
@@ -10585,10 +10585,10 @@
         <v>35674</v>
       </c>
       <c r="G83" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H83" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I83" s="10" t="s">
         <v>189</v>
@@ -10617,10 +10617,10 @@
         <v>35674</v>
       </c>
       <c r="G84" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H84" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I84" s="10" t="s">
         <v>189</v>
@@ -10649,10 +10649,10 @@
         <v>35674</v>
       </c>
       <c r="G85" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H85" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I85" s="10" t="s">
         <v>189</v>
@@ -10681,10 +10681,10 @@
         <v>35674</v>
       </c>
       <c r="G86" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H86" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I86" s="10" t="s">
         <v>189</v>
@@ -10713,10 +10713,10 @@
         <v>35674</v>
       </c>
       <c r="G87" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H87" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I87" s="10" t="s">
         <v>189</v>
@@ -10745,10 +10745,10 @@
         <v>35674</v>
       </c>
       <c r="G88" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H88" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I88" s="10" t="s">
         <v>189</v>
@@ -10777,10 +10777,10 @@
         <v>35674</v>
       </c>
       <c r="G89" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H89" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I89" s="10" t="s">
         <v>189</v>
@@ -10809,10 +10809,10 @@
         <v>35674</v>
       </c>
       <c r="G90" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H90" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I90" s="10" t="s">
         <v>189</v>
@@ -10841,10 +10841,10 @@
         <v>35674</v>
       </c>
       <c r="G91" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H91" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I91" s="10" t="s">
         <v>189</v>
@@ -10873,10 +10873,10 @@
         <v>35674</v>
       </c>
       <c r="G92" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H92" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I92" s="10" t="s">
         <v>189</v>
@@ -10905,10 +10905,10 @@
         <v>35674</v>
       </c>
       <c r="G93" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H93" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I93" s="10" t="s">
         <v>189</v>
@@ -10937,10 +10937,10 @@
         <v>35674</v>
       </c>
       <c r="G94" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H94" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I94" s="10" t="s">
         <v>189</v>
@@ -10969,10 +10969,10 @@
         <v>35674</v>
       </c>
       <c r="G95" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H95" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I95" s="10" t="s">
         <v>189</v>
@@ -11001,10 +11001,10 @@
         <v>35674</v>
       </c>
       <c r="G96" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H96" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I96" s="10" t="s">
         <v>189</v>
@@ -11033,10 +11033,10 @@
         <v>35674</v>
       </c>
       <c r="G97" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H97" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I97" s="10" t="s">
         <v>189</v>
@@ -11065,10 +11065,10 @@
         <v>35674</v>
       </c>
       <c r="G98" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H98" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I98" s="10" t="s">
         <v>189</v>
@@ -11097,10 +11097,10 @@
         <v>35674</v>
       </c>
       <c r="G99" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H99" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I99" s="10" t="s">
         <v>189</v>
@@ -11129,10 +11129,10 @@
         <v>35674</v>
       </c>
       <c r="G100" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H100" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I100" s="10" t="s">
         <v>189</v>
@@ -11161,10 +11161,10 @@
         <v>35674</v>
       </c>
       <c r="G101" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H101" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I101" s="10" t="s">
         <v>189</v>
@@ -11193,10 +11193,10 @@
         <v>35674</v>
       </c>
       <c r="G102" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H102" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I102" s="10" t="s">
         <v>189</v>
@@ -11225,10 +11225,10 @@
         <v>35674</v>
       </c>
       <c r="G103" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H103" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I103" s="10" t="s">
         <v>189</v>
@@ -11257,10 +11257,10 @@
         <v>35674</v>
       </c>
       <c r="G104" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H104" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I104" s="10" t="s">
         <v>189</v>
@@ -11289,10 +11289,10 @@
         <v>35674</v>
       </c>
       <c r="G105" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H105" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I105" s="10" t="s">
         <v>189</v>
@@ -11321,10 +11321,10 @@
         <v>35674</v>
       </c>
       <c r="G106" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H106" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I106" s="10" t="s">
         <v>189</v>
@@ -11353,10 +11353,10 @@
         <v>35674</v>
       </c>
       <c r="G107" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H107" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I107" s="10" t="s">
         <v>189</v>
@@ -11385,10 +11385,10 @@
         <v>35674</v>
       </c>
       <c r="G108" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H108" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I108" s="10" t="s">
         <v>189</v>
@@ -11417,10 +11417,10 @@
         <v>35674</v>
       </c>
       <c r="G109" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H109" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I109" s="10" t="s">
         <v>189</v>
@@ -11449,10 +11449,10 @@
         <v>35674</v>
       </c>
       <c r="G110" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H110" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I110" s="10" t="s">
         <v>189</v>
@@ -11481,10 +11481,10 @@
         <v>35674</v>
       </c>
       <c r="G111" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H111" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I111" s="10" t="s">
         <v>189</v>
@@ -11513,10 +11513,10 @@
         <v>35674</v>
       </c>
       <c r="G112" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H112" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I112" s="10" t="s">
         <v>189</v>
@@ -11545,10 +11545,10 @@
         <v>35674</v>
       </c>
       <c r="G113" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H113" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I113" s="10" t="s">
         <v>189</v>
@@ -11577,10 +11577,10 @@
         <v>35674</v>
       </c>
       <c r="G114" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H114" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I114" s="10" t="s">
         <v>189</v>
@@ -11609,10 +11609,10 @@
         <v>35674</v>
       </c>
       <c r="G115" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H115" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I115" s="10" t="s">
         <v>189</v>
@@ -11641,10 +11641,10 @@
         <v>35674</v>
       </c>
       <c r="G116" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H116" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I116" s="10" t="s">
         <v>189</v>
@@ -11673,10 +11673,10 @@
         <v>35674</v>
       </c>
       <c r="G117" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H117" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I117" s="10" t="s">
         <v>189</v>
@@ -11705,10 +11705,10 @@
         <v>35674</v>
       </c>
       <c r="G118" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H118" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I118" s="10" t="s">
         <v>189</v>
@@ -11737,10 +11737,10 @@
         <v>35674</v>
       </c>
       <c r="G119" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H119" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I119" s="10" t="s">
         <v>189</v>
@@ -11769,10 +11769,10 @@
         <v>35674</v>
       </c>
       <c r="G120" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H120" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I120" s="10" t="s">
         <v>189</v>
@@ -11801,10 +11801,10 @@
         <v>35674</v>
       </c>
       <c r="G121" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H121" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I121" s="10" t="s">
         <v>189</v>
@@ -11833,10 +11833,10 @@
         <v>35674</v>
       </c>
       <c r="G122" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H122" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I122" s="10" t="s">
         <v>189</v>
@@ -11865,10 +11865,10 @@
         <v>35674</v>
       </c>
       <c r="G123" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H123" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I123" s="10" t="s">
         <v>189</v>
@@ -11897,10 +11897,10 @@
         <v>35674</v>
       </c>
       <c r="G124" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H124" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I124" s="10" t="s">
         <v>189</v>
@@ -11929,10 +11929,10 @@
         <v>35674</v>
       </c>
       <c r="G125" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H125" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I125" s="10" t="s">
         <v>189</v>
@@ -11961,10 +11961,10 @@
         <v>35674</v>
       </c>
       <c r="G126" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H126" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I126" s="10" t="s">
         <v>189</v>
@@ -11993,10 +11993,10 @@
         <v>35674</v>
       </c>
       <c r="G127" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H127" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I127" s="10" t="s">
         <v>189</v>
@@ -12025,10 +12025,10 @@
         <v>35674</v>
       </c>
       <c r="G128" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H128" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I128" s="10" t="s">
         <v>189</v>
@@ -12057,10 +12057,10 @@
         <v>35674</v>
       </c>
       <c r="G129" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H129" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I129" s="10" t="s">
         <v>189</v>
@@ -12089,10 +12089,10 @@
         <v>35674</v>
       </c>
       <c r="G130" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H130" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I130" s="10" t="s">
         <v>189</v>
@@ -12121,10 +12121,10 @@
         <v>35674</v>
       </c>
       <c r="G131" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H131" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I131" s="10" t="s">
         <v>189</v>
@@ -12153,10 +12153,10 @@
         <v>35674</v>
       </c>
       <c r="G132" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H132" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I132" s="10" t="s">
         <v>189</v>
@@ -12185,10 +12185,10 @@
         <v>35674</v>
       </c>
       <c r="G133" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H133" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I133" s="10" t="s">
         <v>189</v>
@@ -12217,10 +12217,10 @@
         <v>35674</v>
       </c>
       <c r="G134" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H134" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I134" s="10" t="s">
         <v>189</v>
@@ -12249,10 +12249,10 @@
         <v>35674</v>
       </c>
       <c r="G135" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H135" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I135" s="10" t="s">
         <v>189</v>
@@ -12281,10 +12281,10 @@
         <v>35674</v>
       </c>
       <c r="G136" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H136" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I136" s="10" t="s">
         <v>189</v>
@@ -12313,10 +12313,10 @@
         <v>35674</v>
       </c>
       <c r="G137" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H137" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I137" s="10" t="s">
         <v>189</v>
@@ -12345,10 +12345,10 @@
         <v>35674</v>
       </c>
       <c r="G138" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H138" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I138" s="10" t="s">
         <v>189</v>
@@ -12377,10 +12377,10 @@
         <v>35674</v>
       </c>
       <c r="G139" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H139" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I139" s="10" t="s">
         <v>189</v>
@@ -12409,10 +12409,10 @@
         <v>35674</v>
       </c>
       <c r="G140" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H140" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I140" s="10" t="s">
         <v>189</v>
@@ -12441,10 +12441,10 @@
         <v>35674</v>
       </c>
       <c r="G141" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H141" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I141" s="10" t="s">
         <v>189</v>
@@ -12473,10 +12473,10 @@
         <v>35674</v>
       </c>
       <c r="G142" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H142" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I142" s="10" t="s">
         <v>189</v>
@@ -12505,10 +12505,10 @@
         <v>35674</v>
       </c>
       <c r="G143" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H143" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I143" s="10" t="s">
         <v>189</v>
@@ -12675,7 +12675,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:EC114"/>
+  <dimension ref="A1:EC124"/>
   <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="14.7109375" style="1"/>
@@ -15490,400 +15490,400 @@
         <v>138</v>
       </c>
       <c r="B8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="C8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="D8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="E8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="F8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="G8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="I8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="J8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="K8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="L8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="M8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="N8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="O8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="P8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="Q8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="R8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="S8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="T8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="U8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="V8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="W8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="X8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="Y8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="Z8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AA8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AB8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AC8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AD8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AE8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AF8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AG8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AH8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AI8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AJ8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AK8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AL8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AM8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AN8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AO8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AP8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AQ8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AR8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AS8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AT8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AU8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AV8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AW8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AX8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AY8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AZ8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BA8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BB8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BC8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BD8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BE8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BF8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BG8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BH8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BI8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BJ8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BK8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BL8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BM8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BN8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BO8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BP8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BQ8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BR8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BS8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BT8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BU8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BV8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BW8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BX8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BY8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="BZ8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CA8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CB8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CC8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CD8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CE8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CF8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CG8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CH8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CI8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CJ8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CK8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CL8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CM8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CN8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CO8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CP8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CQ8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CR8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CS8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CT8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CU8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CV8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CW8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CX8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CY8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="CZ8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DA8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DB8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DC8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DD8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DE8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DF8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DG8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DH8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DI8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DJ8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DK8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DL8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DM8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DN8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DO8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DP8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DQ8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DR8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DS8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DT8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DU8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DV8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DW8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DX8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DY8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="DZ8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="EA8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="EB8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="EC8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="9" spans="1:133" x14ac:dyDescent="0.2">
@@ -15891,400 +15891,400 @@
         <v>139</v>
       </c>
       <c r="B9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="J9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="L9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="M9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="N9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="O9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="P9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="Q9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="R9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="S9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="T9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="U9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="V9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="W9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="X9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="Y9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="Z9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AA9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AB9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AC9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AD9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AE9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AF9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AG9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AH9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AI9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AJ9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AK9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AL9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AM9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AN9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AO9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AP9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AQ9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AR9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AS9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AT9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AU9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AV9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AW9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AX9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AY9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AZ9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BA9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BB9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BC9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BD9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BE9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BF9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BG9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BH9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BI9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BJ9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BK9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BL9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BM9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BN9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BO9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BP9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BQ9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BR9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BS9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BT9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BU9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BV9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BW9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BX9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BY9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="BZ9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CA9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CB9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CC9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CD9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CE9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CF9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CG9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CH9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CI9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CJ9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CK9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CL9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CM9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CN9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CO9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CP9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CQ9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CR9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CS9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CT9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CU9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CV9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CW9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CX9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CY9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CZ9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DA9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DB9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DC9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DD9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DE9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DF9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DG9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DH9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DI9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DJ9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DK9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DL9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DM9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DN9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DO9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DP9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DQ9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DR9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DS9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DT9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DU9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DV9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DW9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DX9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DY9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="DZ9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="EA9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="EB9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="EC9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:133" x14ac:dyDescent="0.2">
@@ -57952,6 +57952,4016 @@
         <v>3.6</v>
       </c>
     </row>
+    <row r="115" spans="1:133" x14ac:dyDescent="0.2">
+      <c r="A115" s="9">
+        <v>45170</v>
+      </c>
+      <c r="B115" s="8">
+        <v>146.69999999999999</v>
+      </c>
+      <c r="C115" s="8">
+        <v>148.4</v>
+      </c>
+      <c r="D115" s="8">
+        <v>155.6</v>
+      </c>
+      <c r="E115" s="8">
+        <v>146.6</v>
+      </c>
+      <c r="F115" s="8">
+        <v>146.6</v>
+      </c>
+      <c r="G115" s="8">
+        <v>143.9</v>
+      </c>
+      <c r="H115" s="8">
+        <v>145.9</v>
+      </c>
+      <c r="I115" s="8">
+        <v>146.5</v>
+      </c>
+      <c r="J115" s="8">
+        <v>141.19999999999999</v>
+      </c>
+      <c r="K115" s="8">
+        <v>149</v>
+      </c>
+      <c r="L115" s="8">
+        <v>141.9</v>
+      </c>
+      <c r="M115" s="8">
+        <v>146.9</v>
+      </c>
+      <c r="N115" s="8">
+        <v>142.19999999999999</v>
+      </c>
+      <c r="O115" s="8">
+        <v>147.69999999999999</v>
+      </c>
+      <c r="P115" s="8">
+        <v>151.9</v>
+      </c>
+      <c r="Q115" s="8">
+        <v>158</v>
+      </c>
+      <c r="R115" s="8">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="S115" s="8">
+        <v>146</v>
+      </c>
+      <c r="T115" s="8">
+        <v>147.5</v>
+      </c>
+      <c r="U115" s="8">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="V115" s="8">
+        <v>142.30000000000001</v>
+      </c>
+      <c r="W115" s="8">
+        <v>147.1</v>
+      </c>
+      <c r="X115" s="8">
+        <v>151.4</v>
+      </c>
+      <c r="Y115" s="8">
+        <v>148.9</v>
+      </c>
+      <c r="Z115" s="8">
+        <v>149</v>
+      </c>
+      <c r="AA115" s="8">
+        <v>146.69999999999999</v>
+      </c>
+      <c r="AB115" s="8">
+        <v>148.4</v>
+      </c>
+      <c r="AC115" s="8">
+        <v>153.69999999999999</v>
+      </c>
+      <c r="AD115" s="8">
+        <v>146.6</v>
+      </c>
+      <c r="AE115" s="8">
+        <v>146.6</v>
+      </c>
+      <c r="AF115" s="8">
+        <v>143.80000000000001</v>
+      </c>
+      <c r="AG115" s="8">
+        <v>146</v>
+      </c>
+      <c r="AH115" s="8">
+        <v>147</v>
+      </c>
+      <c r="AI115" s="8">
+        <v>142</v>
+      </c>
+      <c r="AJ115" s="8">
+        <v>149</v>
+      </c>
+      <c r="AK115" s="8">
+        <v>142.30000000000001</v>
+      </c>
+      <c r="AL115" s="8">
+        <v>146.80000000000001</v>
+      </c>
+      <c r="AM115" s="8">
+        <v>142.4</v>
+      </c>
+      <c r="AN115" s="8">
+        <v>147.1</v>
+      </c>
+      <c r="AO115" s="8">
+        <v>151.5</v>
+      </c>
+      <c r="AP115" s="8">
+        <v>154.1</v>
+      </c>
+      <c r="AQ115" s="8">
+        <v>149.69999999999999</v>
+      </c>
+      <c r="AR115" s="8">
+        <v>146.1</v>
+      </c>
+      <c r="AS115" s="8">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="AT115" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="AU115" s="8">
+        <v>1.6</v>
+      </c>
+      <c r="AV115" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="AW115" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="AX115" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="AY115" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="AZ115" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="BA115" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="BB115" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="BC115" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD115" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="BE115" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="BF115" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="BG115" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="BH115" s="8">
+        <v>1</v>
+      </c>
+      <c r="BI115" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="BJ115" s="8">
+        <v>1.6</v>
+      </c>
+      <c r="BK115" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="BL115" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="BM115" s="8">
+        <v>1</v>
+      </c>
+      <c r="BN115" s="8">
+        <v>1</v>
+      </c>
+      <c r="BO115" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="BP115" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BQ115" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BR115" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BS115" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BT115" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="BU115" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BV115" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="BW115" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="BX115" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="BY115" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="BZ115" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="CA115" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="CB115" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="CC115" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="CD115" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="CE115" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="CF115" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="CG115" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="CH115" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="CI115" s="8">
+        <v>1.6</v>
+      </c>
+      <c r="CJ115" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="CK115" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="CL115" s="8">
+        <v>4</v>
+      </c>
+      <c r="CM115" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="CN115" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="CO115" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="CP115" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="CQ115" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="CR115" s="8">
+        <v>5.5</v>
+      </c>
+      <c r="CS115" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="CT115" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="CU115" s="8">
+        <v>3</v>
+      </c>
+      <c r="CV115" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="CW115" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="CX115" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="CY115" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="CZ115" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="DA115" s="8">
+        <v>6</v>
+      </c>
+      <c r="DB115" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="DC115" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DD115" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="DE115" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DF115" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DG115" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="DH115" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DI115" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DJ115" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="DK115" s="8">
+        <v>4</v>
+      </c>
+      <c r="DL115" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="DM115" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="DN115" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="DO115" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="DP115" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="DQ115" s="8">
+        <v>5.5</v>
+      </c>
+      <c r="DR115" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="DS115" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DT115" s="8">
+        <v>3</v>
+      </c>
+      <c r="DU115" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="DV115" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DW115" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="DX115" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="DY115" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DZ115" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="EA115" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="EB115" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="EC115" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="116" spans="1:133" x14ac:dyDescent="0.2">
+      <c r="A116" s="9">
+        <v>45261</v>
+      </c>
+      <c r="B116" s="8">
+        <v>148.6</v>
+      </c>
+      <c r="C116" s="8">
+        <v>150</v>
+      </c>
+      <c r="D116" s="8">
+        <v>157.19999999999999</v>
+      </c>
+      <c r="E116" s="8">
+        <v>147.5</v>
+      </c>
+      <c r="F116" s="8">
+        <v>147.69999999999999</v>
+      </c>
+      <c r="G116" s="8">
+        <v>145.1</v>
+      </c>
+      <c r="H116" s="8">
+        <v>146.30000000000001</v>
+      </c>
+      <c r="I116" s="8">
+        <v>147.19999999999999</v>
+      </c>
+      <c r="J116" s="8">
+        <v>143.1</v>
+      </c>
+      <c r="K116" s="8">
+        <v>150.6</v>
+      </c>
+      <c r="L116" s="8">
+        <v>142.69999999999999</v>
+      </c>
+      <c r="M116" s="8">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="N116" s="8">
+        <v>143</v>
+      </c>
+      <c r="O116" s="8">
+        <v>149.69999999999999</v>
+      </c>
+      <c r="P116" s="8">
+        <v>154</v>
+      </c>
+      <c r="Q116" s="8">
+        <v>159.30000000000001</v>
+      </c>
+      <c r="R116" s="8">
+        <v>150.69999999999999</v>
+      </c>
+      <c r="S116" s="8">
+        <v>147.1</v>
+      </c>
+      <c r="T116" s="8">
+        <v>148.6</v>
+      </c>
+      <c r="U116" s="8">
+        <v>153.9</v>
+      </c>
+      <c r="V116" s="8">
+        <v>143.19999999999999</v>
+      </c>
+      <c r="W116" s="8">
+        <v>148.4</v>
+      </c>
+      <c r="X116" s="8">
+        <v>154.19999999999999</v>
+      </c>
+      <c r="Y116" s="8">
+        <v>151.80000000000001</v>
+      </c>
+      <c r="Z116" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="AA116" s="8">
+        <v>148.6</v>
+      </c>
+      <c r="AB116" s="8">
+        <v>150</v>
+      </c>
+      <c r="AC116" s="8">
+        <v>155.4</v>
+      </c>
+      <c r="AD116" s="8">
+        <v>147.6</v>
+      </c>
+      <c r="AE116" s="8">
+        <v>147.69999999999999</v>
+      </c>
+      <c r="AF116" s="8">
+        <v>145</v>
+      </c>
+      <c r="AG116" s="8">
+        <v>146.30000000000001</v>
+      </c>
+      <c r="AH116" s="8">
+        <v>148.19999999999999</v>
+      </c>
+      <c r="AI116" s="8">
+        <v>143.9</v>
+      </c>
+      <c r="AJ116" s="8">
+        <v>150.6</v>
+      </c>
+      <c r="AK116" s="8">
+        <v>143.19999999999999</v>
+      </c>
+      <c r="AL116" s="8">
+        <v>147.69999999999999</v>
+      </c>
+      <c r="AM116" s="8">
+        <v>143.19999999999999</v>
+      </c>
+      <c r="AN116" s="8">
+        <v>148.5</v>
+      </c>
+      <c r="AO116" s="8">
+        <v>154</v>
+      </c>
+      <c r="AP116" s="8">
+        <v>156.1</v>
+      </c>
+      <c r="AQ116" s="8">
+        <v>150.4</v>
+      </c>
+      <c r="AR116" s="8">
+        <v>147.19999999999999</v>
+      </c>
+      <c r="AS116" s="8">
+        <v>149.19999999999999</v>
+      </c>
+      <c r="AT116" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="AU116" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AV116" s="8">
+        <v>1</v>
+      </c>
+      <c r="AW116" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="AX116" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="AY116" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="AZ116" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="BA116" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BB116" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="BC116" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BD116" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BE116" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BF116" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BG116" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="BH116" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="BI116" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BJ116" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="BK116" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BL116" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BM116" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BN116" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BO116" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="BP116" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="BQ116" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="BR116" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="BS116" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="BT116" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BU116" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BV116" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BW116" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BX116" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BY116" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="BZ116" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="CA116" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="CB116" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="CC116" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="CD116" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="CE116" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="CF116" s="8">
+        <v>1</v>
+      </c>
+      <c r="CG116" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="CH116" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="CI116" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="CJ116" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="CK116" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="CL116" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="CM116" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="CN116" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="CO116" s="8">
+        <v>4</v>
+      </c>
+      <c r="CP116" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CQ116" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="CR116" s="8">
+        <v>4</v>
+      </c>
+      <c r="CS116" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="CT116" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="CU116" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="CV116" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="CW116" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="CX116" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="CY116" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="CZ116" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="DA116" s="8">
+        <v>6.3</v>
+      </c>
+      <c r="DB116" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="DC116" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="DD116" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="DE116" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="DF116" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="DG116" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="DH116" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="DI116" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="DJ116" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="DK116" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="DL116" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="DM116" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DN116" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="DO116" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DP116" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="DQ116" s="8">
+        <v>4</v>
+      </c>
+      <c r="DR116" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="DS116" s="8">
+        <v>4</v>
+      </c>
+      <c r="DT116" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="DU116" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DV116" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DW116" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="DX116" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DY116" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="DZ116" s="8">
+        <v>5.6</v>
+      </c>
+      <c r="EA116" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="EB116" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="EC116" s="8">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:133" x14ac:dyDescent="0.2">
+      <c r="A117" s="9">
+        <v>45352</v>
+      </c>
+      <c r="B117" s="8">
+        <v>149.4</v>
+      </c>
+      <c r="C117" s="8">
+        <v>150.80000000000001</v>
+      </c>
+      <c r="D117" s="8">
+        <v>158.1</v>
+      </c>
+      <c r="E117" s="8">
+        <v>148.69999999999999</v>
+      </c>
+      <c r="F117" s="8">
+        <v>148.9</v>
+      </c>
+      <c r="G117" s="8">
+        <v>145.5</v>
+      </c>
+      <c r="H117" s="8">
+        <v>146.6</v>
+      </c>
+      <c r="I117" s="8">
+        <v>148.19999999999999</v>
+      </c>
+      <c r="J117" s="8">
+        <v>143.19999999999999</v>
+      </c>
+      <c r="K117" s="8">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="L117" s="8">
+        <v>143.19999999999999</v>
+      </c>
+      <c r="M117" s="8">
+        <v>148.9</v>
+      </c>
+      <c r="N117" s="8">
+        <v>144.19999999999999</v>
+      </c>
+      <c r="O117" s="8">
+        <v>150.6</v>
+      </c>
+      <c r="P117" s="8">
+        <v>155.69999999999999</v>
+      </c>
+      <c r="Q117" s="8">
+        <v>159.9</v>
+      </c>
+      <c r="R117" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="S117" s="8">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="T117" s="8">
+        <v>149.6</v>
+      </c>
+      <c r="U117" s="8">
+        <v>157.1</v>
+      </c>
+      <c r="V117" s="8">
+        <v>144.69999999999999</v>
+      </c>
+      <c r="W117" s="8">
+        <v>149</v>
+      </c>
+      <c r="X117" s="8">
+        <v>155.19999999999999</v>
+      </c>
+      <c r="Y117" s="8">
+        <v>152.4</v>
+      </c>
+      <c r="Z117" s="8">
+        <v>152.1</v>
+      </c>
+      <c r="AA117" s="8">
+        <v>149.4</v>
+      </c>
+      <c r="AB117" s="8">
+        <v>150.80000000000001</v>
+      </c>
+      <c r="AC117" s="8">
+        <v>157.4</v>
+      </c>
+      <c r="AD117" s="8">
+        <v>148.69999999999999</v>
+      </c>
+      <c r="AE117" s="8">
+        <v>148.9</v>
+      </c>
+      <c r="AF117" s="8">
+        <v>145.4</v>
+      </c>
+      <c r="AG117" s="8">
+        <v>146.6</v>
+      </c>
+      <c r="AH117" s="8">
+        <v>149.19999999999999</v>
+      </c>
+      <c r="AI117" s="8">
+        <v>144.1</v>
+      </c>
+      <c r="AJ117" s="8">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="AK117" s="8">
+        <v>143.6</v>
+      </c>
+      <c r="AL117" s="8">
+        <v>148.80000000000001</v>
+      </c>
+      <c r="AM117" s="8">
+        <v>144.4</v>
+      </c>
+      <c r="AN117" s="8">
+        <v>149.1</v>
+      </c>
+      <c r="AO117" s="8">
+        <v>155.30000000000001</v>
+      </c>
+      <c r="AP117" s="8">
+        <v>156.69999999999999</v>
+      </c>
+      <c r="AQ117" s="8">
+        <v>150.9</v>
+      </c>
+      <c r="AR117" s="8">
+        <v>148</v>
+      </c>
+      <c r="AS117" s="8">
+        <v>150.1</v>
+      </c>
+      <c r="AT117" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AU117" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AV117" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="AW117" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="AX117" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="AY117" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="AZ117" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="BA117" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BB117" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="BC117" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BD117" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BE117" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BF117" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BG117" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BH117" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BI117" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BJ117" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BK117" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BL117" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BM117" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="BN117" s="8">
+        <v>1</v>
+      </c>
+      <c r="BO117" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BP117" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BQ117" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BR117" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BS117" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BT117" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BU117" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="BV117" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BW117" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BX117" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="BY117" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="BZ117" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="CA117" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="CB117" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="CC117" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="CD117" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="CE117" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="CF117" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="CG117" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="CH117" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="CI117" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="CJ117" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="CK117" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="CL117" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="CM117" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="CN117" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="CO117" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="CP117" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CQ117" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="CR117" s="8">
+        <v>4</v>
+      </c>
+      <c r="CS117" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="CT117" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="CU117" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="CV117" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="CW117" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="CX117" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="CY117" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="CZ117" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="DA117" s="8">
+        <v>6.4</v>
+      </c>
+      <c r="DB117" s="8">
+        <v>3</v>
+      </c>
+      <c r="DC117" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="DD117" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="DE117" s="8">
+        <v>5.5</v>
+      </c>
+      <c r="DF117" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="DG117" s="8">
+        <v>3</v>
+      </c>
+      <c r="DH117" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="DI117" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="DJ117" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DK117" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DL117" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="DM117" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="DN117" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="DO117" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DP117" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="DQ117" s="8">
+        <v>4</v>
+      </c>
+      <c r="DR117" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="DS117" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="DT117" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DU117" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DV117" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DW117" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="DX117" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="DY117" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="DZ117" s="8">
+        <v>5.3</v>
+      </c>
+      <c r="EA117" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="EB117" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="EC117" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:133" x14ac:dyDescent="0.2">
+      <c r="A118" s="9">
+        <v>45444</v>
+      </c>
+      <c r="B118" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="C118" s="8">
+        <v>151.80000000000001</v>
+      </c>
+      <c r="D118" s="8">
+        <v>159.1</v>
+      </c>
+      <c r="E118" s="8">
+        <v>150</v>
+      </c>
+      <c r="F118" s="8">
+        <v>149.9</v>
+      </c>
+      <c r="G118" s="8">
+        <v>145.80000000000001</v>
+      </c>
+      <c r="H118" s="8">
+        <v>147.30000000000001</v>
+      </c>
+      <c r="I118" s="8">
+        <v>149.1</v>
+      </c>
+      <c r="J118" s="8">
+        <v>143.80000000000001</v>
+      </c>
+      <c r="K118" s="8">
+        <v>152.80000000000001</v>
+      </c>
+      <c r="L118" s="8">
+        <v>144</v>
+      </c>
+      <c r="M118" s="8">
+        <v>150</v>
+      </c>
+      <c r="N118" s="8">
+        <v>144.69999999999999</v>
+      </c>
+      <c r="O118" s="8">
+        <v>151</v>
+      </c>
+      <c r="P118" s="8">
+        <v>157</v>
+      </c>
+      <c r="Q118" s="8">
+        <v>160.1</v>
+      </c>
+      <c r="R118" s="8">
+        <v>152.5</v>
+      </c>
+      <c r="S118" s="8">
+        <v>148.19999999999999</v>
+      </c>
+      <c r="T118" s="8">
+        <v>150.4</v>
+      </c>
+      <c r="U118" s="8">
+        <v>158.30000000000001</v>
+      </c>
+      <c r="V118" s="8">
+        <v>146.5</v>
+      </c>
+      <c r="W118" s="8">
+        <v>150.69999999999999</v>
+      </c>
+      <c r="X118" s="8">
+        <v>156.1</v>
+      </c>
+      <c r="Y118" s="8">
+        <v>152.9</v>
+      </c>
+      <c r="Z118" s="8">
+        <v>153.19999999999999</v>
+      </c>
+      <c r="AA118" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="AB118" s="8">
+        <v>151.80000000000001</v>
+      </c>
+      <c r="AC118" s="8">
+        <v>158.5</v>
+      </c>
+      <c r="AD118" s="8">
+        <v>150.1</v>
+      </c>
+      <c r="AE118" s="8">
+        <v>149.9</v>
+      </c>
+      <c r="AF118" s="8">
+        <v>145.69999999999999</v>
+      </c>
+      <c r="AG118" s="8">
+        <v>147.4</v>
+      </c>
+      <c r="AH118" s="8">
+        <v>150.1</v>
+      </c>
+      <c r="AI118" s="8">
+        <v>144.6</v>
+      </c>
+      <c r="AJ118" s="8">
+        <v>152.80000000000001</v>
+      </c>
+      <c r="AK118" s="8">
+        <v>144.5</v>
+      </c>
+      <c r="AL118" s="8">
+        <v>149.9</v>
+      </c>
+      <c r="AM118" s="8">
+        <v>144.9</v>
+      </c>
+      <c r="AN118" s="8">
+        <v>150.69999999999999</v>
+      </c>
+      <c r="AO118" s="8">
+        <v>156.4</v>
+      </c>
+      <c r="AP118" s="8">
+        <v>157</v>
+      </c>
+      <c r="AQ118" s="8">
+        <v>152.1</v>
+      </c>
+      <c r="AR118" s="8">
+        <v>148.4</v>
+      </c>
+      <c r="AS118" s="8">
+        <v>151</v>
+      </c>
+      <c r="AT118" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="AU118" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="AV118" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="AW118" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="AX118" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="AY118" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="AZ118" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BA118" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BB118" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BC118" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BD118" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BE118" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BF118" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="BG118" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="BH118" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BI118" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="BJ118" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BK118" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="BL118" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BM118" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BN118" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="BO118" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BP118" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BQ118" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="BR118" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BS118" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="BT118" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BU118" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BV118" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="BW118" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BX118" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="BY118" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BZ118" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="CA118" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="CB118" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="CC118" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="CD118" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="CE118" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="CF118" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="CG118" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="CH118" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="CI118" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="CJ118" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="CK118" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="CL118" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="CM118" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="CN118" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="CO118" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="CP118" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="CQ118" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="CR118" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="CS118" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="CT118" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CU118" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="CV118" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="CW118" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="CX118" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="CY118" s="8">
+        <v>5</v>
+      </c>
+      <c r="CZ118" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="DA118" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="DB118" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="DC118" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="DD118" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="DE118" s="8">
+        <v>5</v>
+      </c>
+      <c r="DF118" s="8">
+        <v>4</v>
+      </c>
+      <c r="DG118" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="DH118" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="DI118" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="DJ118" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="DK118" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="DL118" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DM118" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="DN118" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="DO118" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="DP118" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="DQ118" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="DR118" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="DS118" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="DT118" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="DU118" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="DV118" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="DW118" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="DX118" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="DY118" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="DZ118" s="8">
+        <v>5</v>
+      </c>
+      <c r="EA118" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="EB118" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="EC118" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="119" spans="1:133" x14ac:dyDescent="0.2">
+      <c r="A119" s="9">
+        <v>45536</v>
+      </c>
+      <c r="B119" s="8">
+        <v>152.30000000000001</v>
+      </c>
+      <c r="C119" s="8">
+        <v>154</v>
+      </c>
+      <c r="D119" s="8">
+        <v>161.5</v>
+      </c>
+      <c r="E119" s="8">
+        <v>151.6</v>
+      </c>
+      <c r="F119" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="G119" s="8">
+        <v>148.69999999999999</v>
+      </c>
+      <c r="H119" s="8">
+        <v>151</v>
+      </c>
+      <c r="I119" s="8">
+        <v>151.80000000000001</v>
+      </c>
+      <c r="J119" s="8">
+        <v>145.9</v>
+      </c>
+      <c r="K119" s="8">
+        <v>153.4</v>
+      </c>
+      <c r="L119" s="8">
+        <v>146.5</v>
+      </c>
+      <c r="M119" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="N119" s="8">
+        <v>147.6</v>
+      </c>
+      <c r="O119" s="8">
+        <v>154.80000000000001</v>
+      </c>
+      <c r="P119" s="8">
+        <v>158.4</v>
+      </c>
+      <c r="Q119" s="8">
+        <v>164.2</v>
+      </c>
+      <c r="R119" s="8">
+        <v>154.6</v>
+      </c>
+      <c r="S119" s="8">
+        <v>150.6</v>
+      </c>
+      <c r="T119" s="8">
+        <v>152.6</v>
+      </c>
+      <c r="U119" s="8">
+        <v>162</v>
+      </c>
+      <c r="V119" s="8">
+        <v>148.1</v>
+      </c>
+      <c r="W119" s="8">
+        <v>151.80000000000001</v>
+      </c>
+      <c r="X119" s="8">
+        <v>158.1</v>
+      </c>
+      <c r="Y119" s="8">
+        <v>153.5</v>
+      </c>
+      <c r="Z119" s="8">
+        <v>154.5</v>
+      </c>
+      <c r="AA119" s="8">
+        <v>152.30000000000001</v>
+      </c>
+      <c r="AB119" s="8">
+        <v>154</v>
+      </c>
+      <c r="AC119" s="8">
+        <v>161.5</v>
+      </c>
+      <c r="AD119" s="8">
+        <v>151.69999999999999</v>
+      </c>
+      <c r="AE119" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="AF119" s="8">
+        <v>148.69999999999999</v>
+      </c>
+      <c r="AG119" s="8">
+        <v>151.1</v>
+      </c>
+      <c r="AH119" s="8">
+        <v>152.30000000000001</v>
+      </c>
+      <c r="AI119" s="8">
+        <v>146.69999999999999</v>
+      </c>
+      <c r="AJ119" s="8">
+        <v>153.5</v>
+      </c>
+      <c r="AK119" s="8">
+        <v>147</v>
+      </c>
+      <c r="AL119" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="AM119" s="8">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="AN119" s="8">
+        <v>152</v>
+      </c>
+      <c r="AO119" s="8">
+        <v>158.19999999999999</v>
+      </c>
+      <c r="AP119" s="8">
+        <v>159.6</v>
+      </c>
+      <c r="AQ119" s="8">
+        <v>154.1</v>
+      </c>
+      <c r="AR119" s="8">
+        <v>150.80000000000001</v>
+      </c>
+      <c r="AS119" s="8">
+        <v>153</v>
+      </c>
+      <c r="AT119" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="AU119" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="AV119" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="AW119" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AX119" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="AY119" s="8">
+        <v>2</v>
+      </c>
+      <c r="AZ119" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="BA119" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="BB119" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="BC119" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BD119" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="BE119" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="BF119" s="8">
+        <v>2</v>
+      </c>
+      <c r="BG119" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="BH119" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="BI119" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="BJ119" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="BK119" s="8">
+        <v>1.6</v>
+      </c>
+      <c r="BL119" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="BM119" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="BN119" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BO119" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BP119" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="BQ119" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BR119" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BS119" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BT119" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="BU119" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="BV119" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BW119" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="BX119" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="BY119" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="BZ119" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="CA119" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="CB119" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="CC119" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="CD119" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="CE119" s="8">
+        <v>2</v>
+      </c>
+      <c r="CF119" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="CG119" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="CH119" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="CI119" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="CJ119" s="8">
+        <v>1.6</v>
+      </c>
+      <c r="CK119" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="CL119" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="CM119" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="CN119" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="CO119" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="CP119" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="CQ119" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CR119" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="CS119" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="CT119" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CU119" s="8">
+        <v>3</v>
+      </c>
+      <c r="CV119" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="CW119" s="8">
+        <v>3</v>
+      </c>
+      <c r="CX119" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="CY119" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="CZ119" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="DA119" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="DB119" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="DC119" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="DD119" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="DE119" s="8">
+        <v>6.4</v>
+      </c>
+      <c r="DF119" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="DG119" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="DH119" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="DI119" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="DJ119" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="DK119" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DL119" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DM119" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="DN119" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="DO119" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="DP119" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="DQ119" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="DR119" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DS119" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DT119" s="8">
+        <v>3</v>
+      </c>
+      <c r="DU119" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DV119" s="8">
+        <v>3</v>
+      </c>
+      <c r="DW119" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DX119" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DY119" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="DZ119" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="EA119" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="EB119" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="EC119" s="8">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:133" x14ac:dyDescent="0.2">
+      <c r="A120" s="9">
+        <v>45627</v>
+      </c>
+      <c r="B120" s="8">
+        <v>153.80000000000001</v>
+      </c>
+      <c r="C120" s="8">
+        <v>155.6</v>
+      </c>
+      <c r="D120" s="8">
+        <v>162.5</v>
+      </c>
+      <c r="E120" s="8">
+        <v>152.69999999999999</v>
+      </c>
+      <c r="F120" s="8">
+        <v>152.5</v>
+      </c>
+      <c r="G120" s="8">
+        <v>149.69999999999999</v>
+      </c>
+      <c r="H120" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="I120" s="8">
+        <v>152.80000000000001</v>
+      </c>
+      <c r="J120" s="8">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="K120" s="8">
+        <v>154.80000000000001</v>
+      </c>
+      <c r="L120" s="8">
+        <v>147.19999999999999</v>
+      </c>
+      <c r="M120" s="8">
+        <v>152</v>
+      </c>
+      <c r="N120" s="8">
+        <v>147.9</v>
+      </c>
+      <c r="O120" s="8">
+        <v>154.69999999999999</v>
+      </c>
+      <c r="P120" s="8">
+        <v>159.30000000000001</v>
+      </c>
+      <c r="Q120" s="8">
+        <v>164.8</v>
+      </c>
+      <c r="R120" s="8">
+        <v>155.30000000000001</v>
+      </c>
+      <c r="S120" s="8">
+        <v>151.4</v>
+      </c>
+      <c r="T120" s="8">
+        <v>153.5</v>
+      </c>
+      <c r="U120" s="8">
+        <v>163.6</v>
+      </c>
+      <c r="V120" s="8">
+        <v>148.6</v>
+      </c>
+      <c r="W120" s="8">
+        <v>152.80000000000001</v>
+      </c>
+      <c r="X120" s="8">
+        <v>159.1</v>
+      </c>
+      <c r="Y120" s="8">
+        <v>154.80000000000001</v>
+      </c>
+      <c r="Z120" s="8">
+        <v>155.69999999999999</v>
+      </c>
+      <c r="AA120" s="8">
+        <v>153.80000000000001</v>
+      </c>
+      <c r="AB120" s="8">
+        <v>155.6</v>
+      </c>
+      <c r="AC120" s="8">
+        <v>162.9</v>
+      </c>
+      <c r="AD120" s="8">
+        <v>152.69999999999999</v>
+      </c>
+      <c r="AE120" s="8">
+        <v>152.5</v>
+      </c>
+      <c r="AF120" s="8">
+        <v>149.6</v>
+      </c>
+      <c r="AG120" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="AH120" s="8">
+        <v>153.69999999999999</v>
+      </c>
+      <c r="AI120" s="8">
+        <v>148.6</v>
+      </c>
+      <c r="AJ120" s="8">
+        <v>154.9</v>
+      </c>
+      <c r="AK120" s="8">
+        <v>147.69999999999999</v>
+      </c>
+      <c r="AL120" s="8">
+        <v>151.9</v>
+      </c>
+      <c r="AM120" s="8">
+        <v>148.19999999999999</v>
+      </c>
+      <c r="AN120" s="8">
+        <v>153</v>
+      </c>
+      <c r="AO120" s="8">
+        <v>159.1</v>
+      </c>
+      <c r="AP120" s="8">
+        <v>160.5</v>
+      </c>
+      <c r="AQ120" s="8">
+        <v>154.80000000000001</v>
+      </c>
+      <c r="AR120" s="8">
+        <v>151.6</v>
+      </c>
+      <c r="AS120" s="8">
+        <v>154</v>
+      </c>
+      <c r="AT120" s="8">
+        <v>1</v>
+      </c>
+      <c r="AU120" s="8">
+        <v>1</v>
+      </c>
+      <c r="AV120" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="AW120" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="AX120" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="AY120" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="AZ120" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="BA120" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BB120" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="BC120" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="BD120" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BE120" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BF120" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="BG120" s="8">
+        <v>-0.1</v>
+      </c>
+      <c r="BH120" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BI120" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BJ120" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BK120" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BL120" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BM120" s="8">
+        <v>1</v>
+      </c>
+      <c r="BN120" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="BO120" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BP120" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BQ120" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BR120" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BS120" s="8">
+        <v>1</v>
+      </c>
+      <c r="BT120" s="8">
+        <v>1</v>
+      </c>
+      <c r="BU120" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="BV120" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BW120" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="BX120" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BY120" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="BZ120" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="CA120" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="CB120" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="CC120" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="CD120" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="CE120" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="CF120" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="CG120" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="CH120" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="CI120" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="CJ120" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="CK120" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="CL120" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="CM120" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="CN120" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="CO120" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="CP120" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="CQ120" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="CR120" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CS120" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="CT120" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CU120" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="CV120" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="CW120" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="CX120" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="CY120" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CZ120" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="DA120" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="DB120" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="DC120" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="DD120" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DE120" s="8">
+        <v>6.3</v>
+      </c>
+      <c r="DF120" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DG120" s="8">
+        <v>3</v>
+      </c>
+      <c r="DH120" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="DI120" s="8">
+        <v>2</v>
+      </c>
+      <c r="DJ120" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="DK120" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="DL120" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="DM120" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="DN120" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="DO120" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="DP120" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="DQ120" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DR120" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="DS120" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DT120" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="DU120" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="DV120" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="DW120" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="DX120" s="8">
+        <v>3</v>
+      </c>
+      <c r="DY120" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DZ120" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="EA120" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="EB120" s="8">
+        <v>3</v>
+      </c>
+      <c r="EC120" s="8">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:133" x14ac:dyDescent="0.2">
+      <c r="A121" s="9">
+        <v>45717</v>
+      </c>
+      <c r="B121" s="8">
+        <v>154.6</v>
+      </c>
+      <c r="C121" s="8">
+        <v>156.1</v>
+      </c>
+      <c r="D121" s="8">
+        <v>164</v>
+      </c>
+      <c r="E121" s="8">
+        <v>153.69999999999999</v>
+      </c>
+      <c r="F121" s="8">
+        <v>153.80000000000001</v>
+      </c>
+      <c r="G121" s="8">
+        <v>149.80000000000001</v>
+      </c>
+      <c r="H121" s="8">
+        <v>151.5</v>
+      </c>
+      <c r="I121" s="8">
+        <v>153.69999999999999</v>
+      </c>
+      <c r="J121" s="8">
+        <v>148.1</v>
+      </c>
+      <c r="K121" s="8">
+        <v>156</v>
+      </c>
+      <c r="L121" s="8">
+        <v>147.9</v>
+      </c>
+      <c r="M121" s="8">
+        <v>153.19999999999999</v>
+      </c>
+      <c r="N121" s="8">
+        <v>148.69999999999999</v>
+      </c>
+      <c r="O121" s="8">
+        <v>155.80000000000001</v>
+      </c>
+      <c r="P121" s="8">
+        <v>161.30000000000001</v>
+      </c>
+      <c r="Q121" s="8">
+        <v>166.7</v>
+      </c>
+      <c r="R121" s="8">
+        <v>155.6</v>
+      </c>
+      <c r="S121" s="8">
+        <v>152.5</v>
+      </c>
+      <c r="T121" s="8">
+        <v>154.5</v>
+      </c>
+      <c r="U121" s="8">
+        <v>164.7</v>
+      </c>
+      <c r="V121" s="8">
+        <v>150.5</v>
+      </c>
+      <c r="W121" s="8">
+        <v>154.4</v>
+      </c>
+      <c r="X121" s="8">
+        <v>161.30000000000001</v>
+      </c>
+      <c r="Y121" s="8">
+        <v>157.19999999999999</v>
+      </c>
+      <c r="Z121" s="8">
+        <v>157.6</v>
+      </c>
+      <c r="AA121" s="8">
+        <v>154.6</v>
+      </c>
+      <c r="AB121" s="8">
+        <v>156.1</v>
+      </c>
+      <c r="AC121" s="8">
+        <v>164.2</v>
+      </c>
+      <c r="AD121" s="8">
+        <v>153.80000000000001</v>
+      </c>
+      <c r="AE121" s="8">
+        <v>153.80000000000001</v>
+      </c>
+      <c r="AF121" s="8">
+        <v>149.69999999999999</v>
+      </c>
+      <c r="AG121" s="8">
+        <v>151.5</v>
+      </c>
+      <c r="AH121" s="8">
+        <v>154.69999999999999</v>
+      </c>
+      <c r="AI121" s="8">
+        <v>148.9</v>
+      </c>
+      <c r="AJ121" s="8">
+        <v>156.1</v>
+      </c>
+      <c r="AK121" s="8">
+        <v>148.4</v>
+      </c>
+      <c r="AL121" s="8">
+        <v>153.1</v>
+      </c>
+      <c r="AM121" s="8">
+        <v>148.9</v>
+      </c>
+      <c r="AN121" s="8">
+        <v>154.5</v>
+      </c>
+      <c r="AO121" s="8">
+        <v>161.19999999999999</v>
+      </c>
+      <c r="AP121" s="8">
+        <v>162.6</v>
+      </c>
+      <c r="AQ121" s="8">
+        <v>155.30000000000001</v>
+      </c>
+      <c r="AR121" s="8">
+        <v>152.6</v>
+      </c>
+      <c r="AS121" s="8">
+        <v>155.19999999999999</v>
+      </c>
+      <c r="AT121" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AU121" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="AV121" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="AW121" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="AX121" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="AY121" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="AZ121" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="BA121" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BB121" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="BC121" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BD121" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BE121" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BF121" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BG121" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BH121" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="BI121" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="BJ121" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="BK121" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BL121" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BM121" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BN121" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="BO121" s="8">
+        <v>1</v>
+      </c>
+      <c r="BP121" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="BQ121" s="8">
+        <v>1.6</v>
+      </c>
+      <c r="BR121" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="BS121" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BT121" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="BU121" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BV121" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BW121" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="BX121" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="BY121" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="BZ121" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="CA121" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="CB121" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="CC121" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="CD121" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="CE121" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="CF121" s="8">
+        <v>1</v>
+      </c>
+      <c r="CG121" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="CH121" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="CI121" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="CJ121" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="CK121" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="CL121" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="CM121" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="CN121" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="CO121" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="CP121" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CQ121" s="8">
+        <v>3</v>
+      </c>
+      <c r="CR121" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CS121" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="CT121" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="CU121" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="CV121" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CW121" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="CX121" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="CY121" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="CZ121" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DA121" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="DB121" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="DC121" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="DD121" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DE121" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="DF121" s="8">
+        <v>4</v>
+      </c>
+      <c r="DG121" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DH121" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="DI121" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="DJ121" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DK121" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="DL121" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="DM121" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="DN121" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="DO121" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DP121" s="8">
+        <v>3</v>
+      </c>
+      <c r="DQ121" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DR121" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="DS121" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DT121" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="DU121" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DV121" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="DW121" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="DX121" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DY121" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DZ121" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="EA121" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="EB121" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="EC121" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:133" x14ac:dyDescent="0.2">
+      <c r="A122" s="9">
+        <v>45809</v>
+      </c>
+      <c r="B122" s="8">
+        <v>156.6</v>
+      </c>
+      <c r="C122" s="8">
+        <v>157</v>
+      </c>
+      <c r="D122" s="8">
+        <v>165.7</v>
+      </c>
+      <c r="E122" s="8">
+        <v>154.6</v>
+      </c>
+      <c r="F122" s="8">
+        <v>154.80000000000001</v>
+      </c>
+      <c r="G122" s="8">
+        <v>150.1</v>
+      </c>
+      <c r="H122" s="8">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="I122" s="8">
+        <v>154.19999999999999</v>
+      </c>
+      <c r="J122" s="8">
+        <v>149.5</v>
+      </c>
+      <c r="K122" s="8">
+        <v>156.69999999999999</v>
+      </c>
+      <c r="L122" s="8">
+        <v>148.9</v>
+      </c>
+      <c r="M122" s="8">
+        <v>154.4</v>
+      </c>
+      <c r="N122" s="8">
+        <v>149.19999999999999</v>
+      </c>
+      <c r="O122" s="8">
+        <v>156</v>
+      </c>
+      <c r="P122" s="8">
+        <v>162.4</v>
+      </c>
+      <c r="Q122" s="8">
+        <v>167.3</v>
+      </c>
+      <c r="R122" s="8">
+        <v>156.9</v>
+      </c>
+      <c r="S122" s="8">
+        <v>153</v>
+      </c>
+      <c r="T122" s="8">
+        <v>155.4</v>
+      </c>
+      <c r="U122" s="8">
+        <v>167.2</v>
+      </c>
+      <c r="V122" s="8">
+        <v>153.69999999999999</v>
+      </c>
+      <c r="W122" s="8">
+        <v>156.30000000000001</v>
+      </c>
+      <c r="X122" s="8">
+        <v>162</v>
+      </c>
+      <c r="Y122" s="8">
+        <v>157.80000000000001</v>
+      </c>
+      <c r="Z122" s="8">
+        <v>158.69999999999999</v>
+      </c>
+      <c r="AA122" s="8">
+        <v>156.6</v>
+      </c>
+      <c r="AB122" s="8">
+        <v>157</v>
+      </c>
+      <c r="AC122" s="8">
+        <v>166.3</v>
+      </c>
+      <c r="AD122" s="8">
+        <v>154.69999999999999</v>
+      </c>
+      <c r="AE122" s="8">
+        <v>154.80000000000001</v>
+      </c>
+      <c r="AF122" s="8">
+        <v>150</v>
+      </c>
+      <c r="AG122" s="8">
+        <v>152.30000000000001</v>
+      </c>
+      <c r="AH122" s="8">
+        <v>155.19999999999999</v>
+      </c>
+      <c r="AI122" s="8">
+        <v>150.19999999999999</v>
+      </c>
+      <c r="AJ122" s="8">
+        <v>156.80000000000001</v>
+      </c>
+      <c r="AK122" s="8">
+        <v>149.4</v>
+      </c>
+      <c r="AL122" s="8">
+        <v>154.4</v>
+      </c>
+      <c r="AM122" s="8">
+        <v>149.5</v>
+      </c>
+      <c r="AN122" s="8">
+        <v>156.19999999999999</v>
+      </c>
+      <c r="AO122" s="8">
+        <v>162</v>
+      </c>
+      <c r="AP122" s="8">
+        <v>163.19999999999999</v>
+      </c>
+      <c r="AQ122" s="8">
+        <v>156.5</v>
+      </c>
+      <c r="AR122" s="8">
+        <v>153.1</v>
+      </c>
+      <c r="AS122" s="8">
+        <v>156.1</v>
+      </c>
+      <c r="AT122" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="AU122" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="AV122" s="8">
+        <v>1</v>
+      </c>
+      <c r="AW122" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="AX122" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="AY122" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="AZ122" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BA122" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="BB122" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="BC122" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BD122" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BE122" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BF122" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="BG122" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="BH122" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BI122" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BJ122" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BK122" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="BL122" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BM122" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="BN122" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="BO122" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="BP122" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BQ122" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BR122" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BS122" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="BT122" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BU122" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="BV122" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BW122" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BX122" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="BY122" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BZ122" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="CA122" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="CB122" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="CC122" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="CD122" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="CE122" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="CF122" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="CG122" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="CH122" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="CI122" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="CJ122" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="CK122" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="CL122" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="CM122" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="CN122" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="CO122" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="CP122" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CQ122" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="CR122" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CS122" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="CT122" s="8">
+        <v>4</v>
+      </c>
+      <c r="CU122" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="CV122" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="CW122" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="CX122" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="CY122" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CZ122" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="DA122" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="DB122" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="DC122" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="DD122" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DE122" s="8">
+        <v>5.6</v>
+      </c>
+      <c r="DF122" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="DG122" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="DH122" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DI122" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="DJ122" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DK122" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="DL122" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="DM122" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="DN122" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="DO122" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DP122" s="8">
+        <v>3</v>
+      </c>
+      <c r="DQ122" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DR122" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="DS122" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="DT122" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="DU122" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="DV122" s="8">
+        <v>3</v>
+      </c>
+      <c r="DW122" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="DX122" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DY122" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DZ122" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="EA122" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="EB122" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="EC122" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:133" x14ac:dyDescent="0.2">
+      <c r="A123" s="9">
+        <v>45901</v>
+      </c>
+      <c r="B123" s="8">
+        <v>157.80000000000001</v>
+      </c>
+      <c r="C123" s="8">
+        <v>158.9</v>
+      </c>
+      <c r="D123" s="8">
+        <v>167.9</v>
+      </c>
+      <c r="E123" s="8">
+        <v>156.5</v>
+      </c>
+      <c r="F123" s="8">
+        <v>156.19999999999999</v>
+      </c>
+      <c r="G123" s="8">
+        <v>153</v>
+      </c>
+      <c r="H123" s="8">
+        <v>155.5</v>
+      </c>
+      <c r="I123" s="8">
+        <v>156</v>
+      </c>
+      <c r="J123" s="8">
+        <v>150.6</v>
+      </c>
+      <c r="K123" s="8">
+        <v>157.4</v>
+      </c>
+      <c r="L123" s="8">
+        <v>151.4</v>
+      </c>
+      <c r="M123" s="8">
+        <v>156.19999999999999</v>
+      </c>
+      <c r="N123" s="8">
+        <v>151.80000000000001</v>
+      </c>
+      <c r="O123" s="8">
+        <v>160.1</v>
+      </c>
+      <c r="P123" s="8">
+        <v>164.4</v>
+      </c>
+      <c r="Q123" s="8">
+        <v>170.9</v>
+      </c>
+      <c r="R123" s="8">
+        <v>159.1</v>
+      </c>
+      <c r="S123" s="8">
+        <v>155.69999999999999</v>
+      </c>
+      <c r="T123" s="8">
+        <v>157.6</v>
+      </c>
+      <c r="U123" s="8">
+        <v>169.1</v>
+      </c>
+      <c r="V123" s="8">
+        <v>154.9</v>
+      </c>
+      <c r="W123" s="8">
+        <v>158.5</v>
+      </c>
+      <c r="X123" s="8">
+        <v>163.5</v>
+      </c>
+      <c r="Y123" s="8">
+        <v>158.6</v>
+      </c>
+      <c r="Z123" s="8">
+        <v>160.4</v>
+      </c>
+      <c r="AA123" s="8">
+        <v>157.80000000000001</v>
+      </c>
+      <c r="AB123" s="8">
+        <v>158.9</v>
+      </c>
+      <c r="AC123" s="8">
+        <v>168.3</v>
+      </c>
+      <c r="AD123" s="8">
+        <v>156.6</v>
+      </c>
+      <c r="AE123" s="8">
+        <v>156.19999999999999</v>
+      </c>
+      <c r="AF123" s="8">
+        <v>152.9</v>
+      </c>
+      <c r="AG123" s="8">
+        <v>155.5</v>
+      </c>
+      <c r="AH123" s="8">
+        <v>157.19999999999999</v>
+      </c>
+      <c r="AI123" s="8">
+        <v>151.4</v>
+      </c>
+      <c r="AJ123" s="8">
+        <v>157.5</v>
+      </c>
+      <c r="AK123" s="8">
+        <v>151.9</v>
+      </c>
+      <c r="AL123" s="8">
+        <v>156.19999999999999</v>
+      </c>
+      <c r="AM123" s="8">
+        <v>152.1</v>
+      </c>
+      <c r="AN123" s="8">
+        <v>158.69999999999999</v>
+      </c>
+      <c r="AO123" s="8">
+        <v>163.80000000000001</v>
+      </c>
+      <c r="AP123" s="8">
+        <v>165.6</v>
+      </c>
+      <c r="AQ123" s="8">
+        <v>159.19999999999999</v>
+      </c>
+      <c r="AR123" s="8">
+        <v>155.80000000000001</v>
+      </c>
+      <c r="AS123" s="8">
+        <v>158.19999999999999</v>
+      </c>
+      <c r="AT123" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="AU123" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="AV123" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="AW123" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="AX123" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="AY123" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="AZ123" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="BA123" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="BB123" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BC123" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BD123" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="BE123" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="BF123" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="BG123" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="BH123" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="BI123" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="BJ123" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="BK123" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="BL123" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="BM123" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BN123" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BO123" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="BP123" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="BQ123" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BR123" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BS123" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BT123" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="BU123" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="BV123" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="BW123" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="BX123" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="BY123" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="BZ123" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="CA123" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="CB123" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="CC123" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="CD123" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="CE123" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="CF123" s="8">
+        <v>1.6</v>
+      </c>
+      <c r="CG123" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="CH123" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="CI123" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="CJ123" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="CK123" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="CL123" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="CM123" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="CN123" s="8">
+        <v>4</v>
+      </c>
+      <c r="CO123" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="CP123" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CQ123" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="CR123" s="8">
+        <v>3</v>
+      </c>
+      <c r="CS123" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="CT123" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="CU123" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="CV123" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CW123" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="CX123" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="CY123" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="CZ123" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DA123" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="DB123" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="DC123" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="DD123" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DE123" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="DF123" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="DG123" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="DH123" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="DI123" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DJ123" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DK123" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DL123" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="DM123" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="DN123" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="DO123" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DP123" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="DQ123" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="DR123" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="DS123" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="DT123" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="DU123" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DV123" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DW123" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="DX123" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="DY123" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="DZ123" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="EA123" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="EB123" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="EC123" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:133" x14ac:dyDescent="0.2">
+      <c r="A124" s="9">
+        <v>45992</v>
+      </c>
+      <c r="B124" s="8">
+        <v>159.5</v>
+      </c>
+      <c r="C124" s="8">
+        <v>160.1</v>
+      </c>
+      <c r="D124" s="8">
+        <v>168.7</v>
+      </c>
+      <c r="E124" s="8">
+        <v>157.6</v>
+      </c>
+      <c r="F124" s="8">
+        <v>157.6</v>
+      </c>
+      <c r="G124" s="8">
+        <v>153.9</v>
+      </c>
+      <c r="H124" s="8">
+        <v>155.80000000000001</v>
+      </c>
+      <c r="I124" s="8">
+        <v>156.9</v>
+      </c>
+      <c r="J124" s="8">
+        <v>152.5</v>
+      </c>
+      <c r="K124" s="8">
+        <v>159</v>
+      </c>
+      <c r="L124" s="8">
+        <v>152.1</v>
+      </c>
+      <c r="M124" s="8">
+        <v>156.9</v>
+      </c>
+      <c r="N124" s="8">
+        <v>152.4</v>
+      </c>
+      <c r="O124" s="8">
+        <v>160.30000000000001</v>
+      </c>
+      <c r="P124" s="8">
+        <v>165.4</v>
+      </c>
+      <c r="Q124" s="8">
+        <v>172.6</v>
+      </c>
+      <c r="R124" s="8">
+        <v>159.9</v>
+      </c>
+      <c r="S124" s="8">
+        <v>156.9</v>
+      </c>
+      <c r="T124" s="8">
+        <v>158.69999999999999</v>
+      </c>
+      <c r="U124" s="8">
+        <v>170.5</v>
+      </c>
+      <c r="V124" s="8">
+        <v>155.6</v>
+      </c>
+      <c r="W124" s="8">
+        <v>159.30000000000001</v>
+      </c>
+      <c r="X124" s="8">
+        <v>164.9</v>
+      </c>
+      <c r="Y124" s="8">
+        <v>160.5</v>
+      </c>
+      <c r="Z124" s="8">
+        <v>161.80000000000001</v>
+      </c>
+      <c r="AA124" s="8">
+        <v>159.5</v>
+      </c>
+      <c r="AB124" s="8">
+        <v>160.1</v>
+      </c>
+      <c r="AC124" s="8">
+        <v>169.4</v>
+      </c>
+      <c r="AD124" s="8">
+        <v>157.69999999999999</v>
+      </c>
+      <c r="AE124" s="8">
+        <v>157.6</v>
+      </c>
+      <c r="AF124" s="8">
+        <v>153.9</v>
+      </c>
+      <c r="AG124" s="8">
+        <v>155.9</v>
+      </c>
+      <c r="AH124" s="8">
+        <v>158.6</v>
+      </c>
+      <c r="AI124" s="8">
+        <v>153.19999999999999</v>
+      </c>
+      <c r="AJ124" s="8">
+        <v>159.1</v>
+      </c>
+      <c r="AK124" s="8">
+        <v>152.6</v>
+      </c>
+      <c r="AL124" s="8">
+        <v>156.9</v>
+      </c>
+      <c r="AM124" s="8">
+        <v>152.69999999999999</v>
+      </c>
+      <c r="AN124" s="8">
+        <v>159.4</v>
+      </c>
+      <c r="AO124" s="8">
+        <v>165</v>
+      </c>
+      <c r="AP124" s="8">
+        <v>167.4</v>
+      </c>
+      <c r="AQ124" s="8">
+        <v>160</v>
+      </c>
+      <c r="AR124" s="8">
+        <v>157</v>
+      </c>
+      <c r="AS124" s="8">
+        <v>159.30000000000001</v>
+      </c>
+      <c r="AT124" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AU124" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="AV124" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AW124" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="AX124" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="AY124" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="AZ124" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="BA124" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BB124" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="BC124" s="8">
+        <v>1</v>
+      </c>
+      <c r="BD124" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BE124" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BF124" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BG124" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="BH124" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BI124" s="8">
+        <v>1</v>
+      </c>
+      <c r="BJ124" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BK124" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BL124" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BM124" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BN124" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BO124" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BP124" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="BQ124" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="BR124" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="BS124" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BT124" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="BU124" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BV124" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BW124" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="BX124" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="BY124" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="BZ124" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="CA124" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="CB124" s="8">
+        <v>1</v>
+      </c>
+      <c r="CC124" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="CD124" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="CE124" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="CF124" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="CG124" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="CH124" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="CI124" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="CJ124" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="CK124" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="CL124" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="CM124" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="CN124" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="CO124" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="CP124" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CQ124" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="CR124" s="8">
+        <v>3</v>
+      </c>
+      <c r="CS124" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="CT124" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="CU124" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="CV124" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CW124" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="CX124" s="8">
+        <v>3</v>
+      </c>
+      <c r="CY124" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="CZ124" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="DA124" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="DB124" s="8">
+        <v>3</v>
+      </c>
+      <c r="DC124" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DD124" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="DE124" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="DF124" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="DG124" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="DH124" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="DI124" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="DJ124" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="DK124" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="DL124" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="DM124" s="8">
+        <v>4</v>
+      </c>
+      <c r="DN124" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DO124" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DP124" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="DQ124" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="DR124" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="DS124" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="DT124" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="DU124" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DV124" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="DW124" s="8">
+        <v>3</v>
+      </c>
+      <c r="DX124" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="DY124" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="DZ124" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="EA124" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="EB124" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="EC124" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
